--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -613,6 +613,12 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['19', '23', '40', '68']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -638,9 +644,6 @@
   </si>
   <si>
     <t>['52']</t>
-  </si>
-  <si>
-    <t>['50']</t>
   </si>
   <si>
     <t>['68']</t>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1438,7 +1441,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1850,7 +1853,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2674,7 +2677,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2752,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8">
         <v>1.89</v>
@@ -3086,7 +3089,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3704,7 +3707,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -4194,10 +4197,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ15">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4322,7 +4325,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4528,7 +4531,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4606,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -4815,7 +4818,7 @@
         <v>3</v>
       </c>
       <c r="AQ18">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5021,7 +5024,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5558,7 +5561,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5970,7 +5973,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6048,7 +6051,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ24">
         <v>1.22</v>
@@ -6176,7 +6179,7 @@
         <v>90</v>
       </c>
       <c r="P25" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>3.25</v>
@@ -6382,7 +6385,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6794,7 +6797,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -7081,7 +7084,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ29">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7905,7 +7908,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ33">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8108,7 +8111,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ34">
         <v>1</v>
@@ -8236,7 +8239,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8442,7 +8445,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8520,7 +8523,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ36">
         <v>1.38</v>
@@ -8648,7 +8651,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8854,7 +8857,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9060,7 +9063,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9141,7 +9144,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9344,7 +9347,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ40">
         <v>1.89</v>
@@ -9472,7 +9475,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9678,7 +9681,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9884,7 +9887,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10168,10 +10171,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ44">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10786,10 +10789,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ47">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11404,7 +11407,7 @@
         <v>3</v>
       </c>
       <c r="AP50">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11819,7 +11822,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ52">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -11944,7 +11947,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12150,7 +12153,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12356,7 +12359,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12643,7 +12646,7 @@
         <v>3</v>
       </c>
       <c r="AQ56">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12768,7 +12771,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12974,7 +12977,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13180,7 +13183,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13258,7 +13261,7 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ59">
         <v>1.22</v>
@@ -13386,7 +13389,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13798,7 +13801,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14004,7 +14007,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14210,7 +14213,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q64">
         <v>2.7</v>
@@ -14494,7 +14497,7 @@
         <v>1.75</v>
       </c>
       <c r="AP65">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ65">
         <v>1.56</v>
@@ -15034,7 +15037,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15115,7 +15118,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ68">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15240,7 +15243,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15446,7 +15449,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15524,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ70">
         <v>1</v>
@@ -15858,7 +15861,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -15939,7 +15942,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ72">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16064,7 +16067,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16270,7 +16273,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16476,7 +16479,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16682,7 +16685,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -17172,7 +17175,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ78">
         <v>1.44</v>
@@ -17300,7 +17303,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17381,7 +17384,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ79">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17506,7 +17509,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17712,7 +17715,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18536,7 +18539,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18617,7 +18620,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18742,7 +18745,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19360,7 +19363,7 @@
         <v>158</v>
       </c>
       <c r="P89" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19438,10 +19441,10 @@
         <v>0.75</v>
       </c>
       <c r="AP89">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19566,7 +19569,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19644,7 +19647,7 @@
         <v>0.2</v>
       </c>
       <c r="AP90">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ90">
         <v>1</v>
@@ -19978,7 +19981,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20596,7 +20599,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20802,7 +20805,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20880,7 +20883,7 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ96">
         <v>1.11</v>
@@ -21214,7 +21217,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21501,7 +21504,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ99">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -21707,7 +21710,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ100">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -22244,7 +22247,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22450,7 +22453,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22528,7 +22531,7 @@
         <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ104">
         <v>1.11</v>
@@ -22940,7 +22943,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ106">
         <v>0.89</v>
@@ -23149,7 +23152,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ107">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23274,7 +23277,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -24098,7 +24101,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24510,7 +24513,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24922,7 +24925,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25334,7 +25337,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25621,7 +25624,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ119">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -25952,7 +25955,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26030,7 +26033,7 @@
         <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ121">
         <v>1.11</v>
@@ -26239,7 +26242,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26648,7 +26651,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ124">
         <v>1.22</v>
@@ -26854,7 +26857,7 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ125">
         <v>1</v>
@@ -27063,7 +27066,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ126">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -28630,7 +28633,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28711,7 +28714,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ134">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -28836,7 +28839,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29326,7 +29329,7 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ137">
         <v>1.33</v>
@@ -29535,7 +29538,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -29866,7 +29869,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30072,7 +30075,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30565,7 +30568,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ143">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -30896,7 +30899,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31102,7 +31105,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31308,7 +31311,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31514,7 +31517,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31720,7 +31723,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32004,7 +32007,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AQ150">
         <v>1.44</v>
@@ -32132,7 +32135,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32210,7 +32213,7 @@
         <v>1.14</v>
       </c>
       <c r="AP151">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ151">
         <v>1.38</v>
@@ -32544,7 +32547,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32956,7 +32959,7 @@
         <v>90</v>
       </c>
       <c r="P155" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q155">
         <v>4.5</v>
@@ -33368,7 +33371,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33574,7 +33577,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33780,7 +33783,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33937,6 +33940,624 @@
       </c>
       <c r="BP159">
         <v>1.23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7469019</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F160">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>76</v>
+      </c>
+      <c r="H160" t="s">
+        <v>74</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>1</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>1</v>
+      </c>
+      <c r="O160" t="s">
+        <v>90</v>
+      </c>
+      <c r="P160" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q160">
+        <v>2.75</v>
+      </c>
+      <c r="R160">
+        <v>2.1</v>
+      </c>
+      <c r="S160">
+        <v>3.75</v>
+      </c>
+      <c r="T160">
+        <v>1.41</v>
+      </c>
+      <c r="U160">
+        <v>2.7</v>
+      </c>
+      <c r="V160">
+        <v>2.95</v>
+      </c>
+      <c r="W160">
+        <v>1.35</v>
+      </c>
+      <c r="X160">
+        <v>7.4</v>
+      </c>
+      <c r="Y160">
+        <v>1.06</v>
+      </c>
+      <c r="Z160">
+        <v>2.1</v>
+      </c>
+      <c r="AA160">
+        <v>3.5</v>
+      </c>
+      <c r="AB160">
+        <v>3.25</v>
+      </c>
+      <c r="AC160">
+        <v>1.06</v>
+      </c>
+      <c r="AD160">
+        <v>8.5</v>
+      </c>
+      <c r="AE160">
+        <v>1.33</v>
+      </c>
+      <c r="AF160">
+        <v>3.2</v>
+      </c>
+      <c r="AG160">
+        <v>1.9</v>
+      </c>
+      <c r="AH160">
+        <v>1.77</v>
+      </c>
+      <c r="AI160">
+        <v>1.8</v>
+      </c>
+      <c r="AJ160">
+        <v>1.95</v>
+      </c>
+      <c r="AK160">
+        <v>1.3</v>
+      </c>
+      <c r="AL160">
+        <v>1.25</v>
+      </c>
+      <c r="AM160">
+        <v>1.7</v>
+      </c>
+      <c r="AN160">
+        <v>1.22</v>
+      </c>
+      <c r="AO160">
+        <v>0.5</v>
+      </c>
+      <c r="AP160">
+        <v>1.1</v>
+      </c>
+      <c r="AQ160">
+        <v>0.78</v>
+      </c>
+      <c r="AR160">
+        <v>1.38</v>
+      </c>
+      <c r="AS160">
+        <v>1.33</v>
+      </c>
+      <c r="AT160">
+        <v>2.71</v>
+      </c>
+      <c r="AU160">
+        <v>4</v>
+      </c>
+      <c r="AV160">
+        <v>14</v>
+      </c>
+      <c r="AW160">
+        <v>4</v>
+      </c>
+      <c r="AX160">
+        <v>10</v>
+      </c>
+      <c r="AY160">
+        <v>8</v>
+      </c>
+      <c r="AZ160">
+        <v>24</v>
+      </c>
+      <c r="BA160">
+        <v>8</v>
+      </c>
+      <c r="BB160">
+        <v>7</v>
+      </c>
+      <c r="BC160">
+        <v>15</v>
+      </c>
+      <c r="BD160">
+        <v>1.74</v>
+      </c>
+      <c r="BE160">
+        <v>6.4</v>
+      </c>
+      <c r="BF160">
+        <v>2.33</v>
+      </c>
+      <c r="BG160">
+        <v>1.38</v>
+      </c>
+      <c r="BH160">
+        <v>2.7</v>
+      </c>
+      <c r="BI160">
+        <v>1.67</v>
+      </c>
+      <c r="BJ160">
+        <v>2.07</v>
+      </c>
+      <c r="BK160">
+        <v>2.08</v>
+      </c>
+      <c r="BL160">
+        <v>1.66</v>
+      </c>
+      <c r="BM160">
+        <v>2.65</v>
+      </c>
+      <c r="BN160">
+        <v>1.41</v>
+      </c>
+      <c r="BO160">
+        <v>3.55</v>
+      </c>
+      <c r="BP160">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7469023</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F161">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>85</v>
+      </c>
+      <c r="H161" t="s">
+        <v>73</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>1</v>
+      </c>
+      <c r="O161" t="s">
+        <v>199</v>
+      </c>
+      <c r="P161" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q161">
+        <v>2.25</v>
+      </c>
+      <c r="R161">
+        <v>2.15</v>
+      </c>
+      <c r="S161">
+        <v>5</v>
+      </c>
+      <c r="T161">
+        <v>1.43</v>
+      </c>
+      <c r="U161">
+        <v>2.65</v>
+      </c>
+      <c r="V161">
+        <v>2.95</v>
+      </c>
+      <c r="W161">
+        <v>1.35</v>
+      </c>
+      <c r="X161">
+        <v>7.4</v>
+      </c>
+      <c r="Y161">
+        <v>1.06</v>
+      </c>
+      <c r="Z161">
+        <v>1.66</v>
+      </c>
+      <c r="AA161">
+        <v>3.7</v>
+      </c>
+      <c r="AB161">
+        <v>5</v>
+      </c>
+      <c r="AC161">
+        <v>1.06</v>
+      </c>
+      <c r="AD161">
+        <v>8.5</v>
+      </c>
+      <c r="AE161">
+        <v>1.33</v>
+      </c>
+      <c r="AF161">
+        <v>3.1</v>
+      </c>
+      <c r="AG161">
+        <v>2</v>
+      </c>
+      <c r="AH161">
+        <v>1.7</v>
+      </c>
+      <c r="AI161">
+        <v>2</v>
+      </c>
+      <c r="AJ161">
+        <v>1.75</v>
+      </c>
+      <c r="AK161">
+        <v>1.11</v>
+      </c>
+      <c r="AL161">
+        <v>1.2</v>
+      </c>
+      <c r="AM161">
+        <v>2.2</v>
+      </c>
+      <c r="AN161">
+        <v>1.75</v>
+      </c>
+      <c r="AO161">
+        <v>0.75</v>
+      </c>
+      <c r="AP161">
+        <v>1.89</v>
+      </c>
+      <c r="AQ161">
+        <v>0.67</v>
+      </c>
+      <c r="AR161">
+        <v>1.88</v>
+      </c>
+      <c r="AS161">
+        <v>1.31</v>
+      </c>
+      <c r="AT161">
+        <v>3.19</v>
+      </c>
+      <c r="AU161">
+        <v>6</v>
+      </c>
+      <c r="AV161">
+        <v>4</v>
+      </c>
+      <c r="AW161">
+        <v>15</v>
+      </c>
+      <c r="AX161">
+        <v>7</v>
+      </c>
+      <c r="AY161">
+        <v>21</v>
+      </c>
+      <c r="AZ161">
+        <v>11</v>
+      </c>
+      <c r="BA161">
+        <v>13</v>
+      </c>
+      <c r="BB161">
+        <v>2</v>
+      </c>
+      <c r="BC161">
+        <v>15</v>
+      </c>
+      <c r="BD161">
+        <v>1.53</v>
+      </c>
+      <c r="BE161">
+        <v>6.4</v>
+      </c>
+      <c r="BF161">
+        <v>2.8</v>
+      </c>
+      <c r="BG161">
+        <v>1.44</v>
+      </c>
+      <c r="BH161">
+        <v>2.55</v>
+      </c>
+      <c r="BI161">
+        <v>1.74</v>
+      </c>
+      <c r="BJ161">
+        <v>1.97</v>
+      </c>
+      <c r="BK161">
+        <v>2.18</v>
+      </c>
+      <c r="BL161">
+        <v>1.58</v>
+      </c>
+      <c r="BM161">
+        <v>2.8</v>
+      </c>
+      <c r="BN161">
+        <v>1.36</v>
+      </c>
+      <c r="BO161">
+        <v>3.8</v>
+      </c>
+      <c r="BP161">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7469024</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F162">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>83</v>
+      </c>
+      <c r="H162" t="s">
+        <v>71</v>
+      </c>
+      <c r="I162">
+        <v>3</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>3</v>
+      </c>
+      <c r="L162">
+        <v>4</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>4</v>
+      </c>
+      <c r="O162" t="s">
+        <v>200</v>
+      </c>
+      <c r="P162" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q162">
+        <v>2.3</v>
+      </c>
+      <c r="R162">
+        <v>1.95</v>
+      </c>
+      <c r="S162">
+        <v>5.75</v>
+      </c>
+      <c r="T162">
+        <v>1.55</v>
+      </c>
+      <c r="U162">
+        <v>2.3</v>
+      </c>
+      <c r="V162">
+        <v>3.55</v>
+      </c>
+      <c r="W162">
+        <v>1.25</v>
+      </c>
+      <c r="X162">
+        <v>9.9</v>
+      </c>
+      <c r="Y162">
+        <v>1.02</v>
+      </c>
+      <c r="Z162">
+        <v>1.65</v>
+      </c>
+      <c r="AA162">
+        <v>3.4</v>
+      </c>
+      <c r="AB162">
+        <v>5.75</v>
+      </c>
+      <c r="AC162">
+        <v>1.1</v>
+      </c>
+      <c r="AD162">
+        <v>6.5</v>
+      </c>
+      <c r="AE162">
+        <v>1.5</v>
+      </c>
+      <c r="AF162">
+        <v>2.4</v>
+      </c>
+      <c r="AG162">
+        <v>2.5</v>
+      </c>
+      <c r="AH162">
+        <v>1.47</v>
+      </c>
+      <c r="AI162">
+        <v>2.38</v>
+      </c>
+      <c r="AJ162">
+        <v>1.5</v>
+      </c>
+      <c r="AK162">
+        <v>1.12</v>
+      </c>
+      <c r="AL162">
+        <v>1.25</v>
+      </c>
+      <c r="AM162">
+        <v>2.15</v>
+      </c>
+      <c r="AN162">
+        <v>1.75</v>
+      </c>
+      <c r="AO162">
+        <v>0.13</v>
+      </c>
+      <c r="AP162">
+        <v>1.89</v>
+      </c>
+      <c r="AQ162">
+        <v>0.11</v>
+      </c>
+      <c r="AR162">
+        <v>1.68</v>
+      </c>
+      <c r="AS162">
+        <v>1.05</v>
+      </c>
+      <c r="AT162">
+        <v>2.73</v>
+      </c>
+      <c r="AU162">
+        <v>8</v>
+      </c>
+      <c r="AV162">
+        <v>4</v>
+      </c>
+      <c r="AW162">
+        <v>7</v>
+      </c>
+      <c r="AX162">
+        <v>4</v>
+      </c>
+      <c r="AY162">
+        <v>15</v>
+      </c>
+      <c r="AZ162">
+        <v>8</v>
+      </c>
+      <c r="BA162">
+        <v>2</v>
+      </c>
+      <c r="BB162">
+        <v>2</v>
+      </c>
+      <c r="BC162">
+        <v>4</v>
+      </c>
+      <c r="BD162">
+        <v>1.49</v>
+      </c>
+      <c r="BE162">
+        <v>6.75</v>
+      </c>
+      <c r="BF162">
+        <v>2.9</v>
+      </c>
+      <c r="BG162">
+        <v>1.42</v>
+      </c>
+      <c r="BH162">
+        <v>2.65</v>
+      </c>
+      <c r="BI162">
+        <v>1.71</v>
+      </c>
+      <c r="BJ162">
+        <v>2</v>
+      </c>
+      <c r="BK162">
+        <v>2.12</v>
+      </c>
+      <c r="BL162">
+        <v>1.63</v>
+      </c>
+      <c r="BM162">
+        <v>2.7</v>
+      </c>
+      <c r="BN162">
+        <v>1.4</v>
+      </c>
+      <c r="BO162">
+        <v>3.65</v>
+      </c>
+      <c r="BP162">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="270">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1185,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3788,7 +3788,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ13">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4815,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ18">
         <v>0.78</v>
@@ -7287,7 +7287,7 @@
         <v>1.5</v>
       </c>
       <c r="AP30">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ30">
         <v>1.1</v>
@@ -8526,7 +8526,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ36">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR36">
         <v>1.66</v>
@@ -12643,7 +12643,7 @@
         <v>0.33</v>
       </c>
       <c r="AP56">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ56">
         <v>0.11</v>
@@ -14088,7 +14088,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ63">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR63">
         <v>1.33</v>
@@ -16972,7 +16972,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ77">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
         <v>1.29</v>
@@ -17587,7 +17587,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ80">
         <v>1.22</v>
@@ -20268,7 +20268,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ93">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR93">
         <v>1.43</v>
@@ -20677,7 +20677,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ95">
         <v>1</v>
@@ -23358,7 +23358,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ108">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR108">
         <v>1.07</v>
@@ -25003,7 +25003,7 @@
         <v>1.2</v>
       </c>
       <c r="AP116">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ116">
         <v>1.33</v>
@@ -25830,7 +25830,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ120">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR120">
         <v>1.24</v>
@@ -27475,7 +27475,7 @@
         <v>1</v>
       </c>
       <c r="AP128">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ128">
         <v>1</v>
@@ -30359,7 +30359,7 @@
         <v>2.13</v>
       </c>
       <c r="AP142">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ142">
         <v>1.89</v>
@@ -30774,7 +30774,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ144">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR144">
         <v>1.43</v>
@@ -34557,6 +34557,212 @@
         <v>3.65</v>
       </c>
       <c r="BP162">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7469021</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45668.66666666666</v>
+      </c>
+      <c r="F163">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>86</v>
+      </c>
+      <c r="H163" t="s">
+        <v>78</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163" t="s">
+        <v>90</v>
+      </c>
+      <c r="P163" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q163">
+        <v>2.5</v>
+      </c>
+      <c r="R163">
+        <v>2.1</v>
+      </c>
+      <c r="S163">
+        <v>4.2</v>
+      </c>
+      <c r="T163">
+        <v>1.38</v>
+      </c>
+      <c r="U163">
+        <v>2.8</v>
+      </c>
+      <c r="V163">
+        <v>2.75</v>
+      </c>
+      <c r="W163">
+        <v>1.4</v>
+      </c>
+      <c r="X163">
+        <v>6.55</v>
+      </c>
+      <c r="Y163">
+        <v>1.08</v>
+      </c>
+      <c r="Z163">
+        <v>1.95</v>
+      </c>
+      <c r="AA163">
+        <v>3.5</v>
+      </c>
+      <c r="AB163">
+        <v>3.88</v>
+      </c>
+      <c r="AC163">
+        <v>1.05</v>
+      </c>
+      <c r="AD163">
+        <v>9</v>
+      </c>
+      <c r="AE163">
+        <v>1.3</v>
+      </c>
+      <c r="AF163">
+        <v>3.45</v>
+      </c>
+      <c r="AG163">
+        <v>1.85</v>
+      </c>
+      <c r="AH163">
+        <v>1.89</v>
+      </c>
+      <c r="AI163">
+        <v>1.7</v>
+      </c>
+      <c r="AJ163">
+        <v>2</v>
+      </c>
+      <c r="AK163">
+        <v>1.25</v>
+      </c>
+      <c r="AL163">
+        <v>1.25</v>
+      </c>
+      <c r="AM163">
+        <v>1.83</v>
+      </c>
+      <c r="AN163">
+        <v>3</v>
+      </c>
+      <c r="AO163">
+        <v>1.38</v>
+      </c>
+      <c r="AP163">
+        <v>2.78</v>
+      </c>
+      <c r="AQ163">
+        <v>1.33</v>
+      </c>
+      <c r="AR163">
+        <v>1.75</v>
+      </c>
+      <c r="AS163">
+        <v>1.39</v>
+      </c>
+      <c r="AT163">
+        <v>3.14</v>
+      </c>
+      <c r="AU163">
+        <v>0</v>
+      </c>
+      <c r="AV163">
+        <v>2</v>
+      </c>
+      <c r="AW163">
+        <v>6</v>
+      </c>
+      <c r="AX163">
+        <v>4</v>
+      </c>
+      <c r="AY163">
+        <v>6</v>
+      </c>
+      <c r="AZ163">
+        <v>6</v>
+      </c>
+      <c r="BA163">
+        <v>3</v>
+      </c>
+      <c r="BB163">
+        <v>3</v>
+      </c>
+      <c r="BC163">
+        <v>6</v>
+      </c>
+      <c r="BD163">
+        <v>1.66</v>
+      </c>
+      <c r="BE163">
+        <v>6.4</v>
+      </c>
+      <c r="BF163">
+        <v>2.48</v>
+      </c>
+      <c r="BG163">
+        <v>1.41</v>
+      </c>
+      <c r="BH163">
+        <v>2.65</v>
+      </c>
+      <c r="BI163">
+        <v>1.68</v>
+      </c>
+      <c r="BJ163">
+        <v>2.02</v>
+      </c>
+      <c r="BK163">
+        <v>2.08</v>
+      </c>
+      <c r="BL163">
+        <v>1.65</v>
+      </c>
+      <c r="BM163">
+        <v>2.7</v>
+      </c>
+      <c r="BN163">
+        <v>1.4</v>
+      </c>
+      <c r="BO163">
+        <v>3.55</v>
+      </c>
+      <c r="BP163">
         <v>1.24</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -33058,16 +33058,16 @@
         <v>9</v>
       </c>
       <c r="AW155">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX155">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY155">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ155">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA155">
         <v>4</v>
@@ -33258,7 +33258,7 @@
         <v>2.76</v>
       </c>
       <c r="AU156">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV156">
         <v>5</v>
@@ -33267,13 +33267,13 @@
         <v>9</v>
       </c>
       <c r="AX156">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY156">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ156">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA156">
         <v>4</v>
@@ -33464,16 +33464,16 @@
         <v>3.13</v>
       </c>
       <c r="AU157">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW157">
+        <v>3</v>
+      </c>
+      <c r="AX157">
         <v>5</v>
-      </c>
-      <c r="AX157">
-        <v>10</v>
       </c>
       <c r="AY157">
         <v>11</v>
@@ -33676,10 +33676,10 @@
         <v>5</v>
       </c>
       <c r="AW158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY158">
         <v>10</v>
@@ -33876,19 +33876,19 @@
         <v>2.83</v>
       </c>
       <c r="AU159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV159">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW159">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AX159">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY159">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ159">
         <v>16</v>
@@ -34085,19 +34085,19 @@
         <v>4</v>
       </c>
       <c r="AV160">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AW160">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX160">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY160">
         <v>8</v>
       </c>
       <c r="AZ160">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA160">
         <v>8</v>
@@ -34291,13 +34291,13 @@
         <v>6</v>
       </c>
       <c r="AV161">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW161">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AX161">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY161">
         <v>21</v>
@@ -34497,13 +34497,13 @@
         <v>8</v>
       </c>
       <c r="AV162">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW162">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AX162">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY162">
         <v>15</v>
@@ -34700,22 +34700,22 @@
         <v>3.14</v>
       </c>
       <c r="AU163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW163">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX163">
         <v>4</v>
       </c>
       <c r="AY163">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ163">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA163">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -619,6 +619,24 @@
     <t>['19', '23', '40', '68']</t>
   </si>
   <si>
+    <t>['5', '71', '90+5']</t>
+  </si>
+  <si>
+    <t>['90+5']</t>
+  </si>
+  <si>
+    <t>['82']</t>
+  </si>
+  <si>
+    <t>['70', '83']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['16', '55', '71']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -703,9 +721,6 @@
     <t>['78']</t>
   </si>
   <si>
-    <t>['51']</t>
-  </si>
-  <si>
     <t>['44']</t>
   </si>
   <si>
@@ -743,9 +758,6 @@
   </si>
   <si>
     <t>['32', '56', '85']</t>
-  </si>
-  <si>
-    <t>['82']</t>
   </si>
   <si>
     <t>['45+4']</t>
@@ -824,6 +836,9 @@
   </si>
   <si>
     <t>['8', '47', '83', '90+1']</t>
+  </si>
+  <si>
+    <t>['20', '61', '70']</t>
   </si>
 </sst>
 </file>
@@ -1185,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP163"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1441,7 +1456,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1519,10 +1534,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ2">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1725,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ3">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1853,7 +1868,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -1931,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ4">
         <v>1.22</v>
@@ -2137,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
         <v>1.1</v>
@@ -2343,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ6">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2549,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1</v>
@@ -2677,7 +2692,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2758,7 +2773,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ8">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2964,7 +2979,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ9">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3089,7 +3104,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3167,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ10">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3707,7 +3722,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3994,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4325,7 +4340,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4406,7 +4421,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4531,7 +4546,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -5021,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19">
         <v>0.11</v>
@@ -5227,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ20">
         <v>1</v>
@@ -5433,10 +5448,10 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ21">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR21">
         <v>1.81</v>
@@ -5561,7 +5576,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5639,7 +5654,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>1.1</v>
@@ -5845,10 +5860,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ23">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>2.13</v>
@@ -5973,7 +5988,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6260,7 +6275,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ25">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR25">
         <v>0.67</v>
@@ -6385,7 +6400,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6463,10 +6478,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -6669,10 +6684,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR27">
         <v>1.55</v>
@@ -6797,7 +6812,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6875,10 +6890,10 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ28">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR28">
         <v>1.92</v>
@@ -7493,7 +7508,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ31">
         <v>1</v>
@@ -7702,7 +7717,7 @@
         <v>2</v>
       </c>
       <c r="AQ32">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR32">
         <v>0.82</v>
@@ -8239,7 +8254,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8445,7 +8460,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8651,7 +8666,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8729,10 +8744,10 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR37">
         <v>1.13</v>
@@ -8857,7 +8872,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -8938,7 +8953,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ38">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR38">
         <v>1.59</v>
@@ -9063,7 +9078,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9350,7 +9365,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ40">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR40">
         <v>1.41</v>
@@ -9475,7 +9490,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9553,7 +9568,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ41">
         <v>1.22</v>
@@ -9681,7 +9696,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9759,10 +9774,10 @@
         <v>1</v>
       </c>
       <c r="AP42">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ42">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -9887,7 +9902,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -9965,10 +9980,10 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR43">
         <v>0.8</v>
@@ -10377,7 +10392,7 @@
         <v>3</v>
       </c>
       <c r="AP45">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ45">
         <v>1.44</v>
@@ -10583,10 +10598,10 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR46">
         <v>1.88</v>
@@ -11201,10 +11216,10 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ49">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR49">
         <v>1.53</v>
@@ -11616,7 +11631,7 @@
         <v>2</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR51">
         <v>1.48</v>
@@ -11819,7 +11834,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ52">
         <v>0.78</v>
@@ -11947,7 +11962,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12025,10 +12040,10 @@
         <v>2</v>
       </c>
       <c r="AP53">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ53">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR53">
         <v>1.76</v>
@@ -12153,7 +12168,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12231,7 +12246,7 @@
         <v>1</v>
       </c>
       <c r="AP54">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ54">
         <v>1.1</v>
@@ -12359,7 +12374,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12440,7 +12455,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ55">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR55">
         <v>1.98</v>
@@ -12771,7 +12786,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12852,7 +12867,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ57">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -12977,7 +12992,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13183,7 +13198,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13389,7 +13404,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13467,10 +13482,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ60">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.51</v>
@@ -13673,7 +13688,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ61">
         <v>1.44</v>
@@ -13801,7 +13816,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -13879,10 +13894,10 @@
         <v>2</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ62">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR62">
         <v>1.16</v>
@@ -14007,7 +14022,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14213,7 +14228,7 @@
         <v>139</v>
       </c>
       <c r="P64" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="Q64">
         <v>2.7</v>
@@ -14291,10 +14306,10 @@
         <v>0</v>
       </c>
       <c r="AP64">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR64">
         <v>1.73</v>
@@ -14500,7 +14515,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ65">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.6</v>
@@ -14909,7 +14924,7 @@
         <v>0.25</v>
       </c>
       <c r="AP67">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15037,7 +15052,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15243,7 +15258,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15321,10 +15336,10 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ69">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR69">
         <v>1.23</v>
@@ -15449,7 +15464,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15530,7 +15545,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ70">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR70">
         <v>1.55</v>
@@ -15733,7 +15748,7 @@
         <v>2</v>
       </c>
       <c r="AP71">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ71">
         <v>1.33</v>
@@ -15861,7 +15876,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -15939,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ72">
         <v>0.67</v>
@@ -16067,7 +16082,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16148,7 +16163,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ73">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1</v>
@@ -16273,7 +16288,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16351,10 +16366,10 @@
         <v>0.5</v>
       </c>
       <c r="AP74">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16479,7 +16494,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16557,10 +16572,10 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ75">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR75">
         <v>1.25</v>
@@ -16685,7 +16700,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16969,7 +16984,7 @@
         <v>2</v>
       </c>
       <c r="AP77">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>1.33</v>
@@ -17303,7 +17318,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17381,7 +17396,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.11</v>
@@ -17509,7 +17524,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17715,7 +17730,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -17796,7 +17811,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ81">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR81">
         <v>1.22</v>
@@ -18002,7 +18017,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR82">
         <v>1.57</v>
@@ -18205,7 +18220,7 @@
         <v>0.8</v>
       </c>
       <c r="AP83">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ83">
         <v>1.1</v>
@@ -18414,7 +18429,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ84">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR84">
         <v>1.51</v>
@@ -18539,7 +18554,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18745,7 +18760,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18826,7 +18841,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR86">
         <v>1.88</v>
@@ -19029,10 +19044,10 @@
         <v>1</v>
       </c>
       <c r="AP87">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ87">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR87">
         <v>1.28</v>
@@ -19235,7 +19250,7 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ88">
         <v>1.33</v>
@@ -19363,7 +19378,7 @@
         <v>158</v>
       </c>
       <c r="P89" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>2.5</v>
@@ -19569,7 +19584,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19856,7 +19871,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -19981,7 +19996,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20265,7 +20280,7 @@
         <v>1.5</v>
       </c>
       <c r="AP93">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ93">
         <v>1.33</v>
@@ -20471,7 +20486,7 @@
         <v>1.2</v>
       </c>
       <c r="AP94">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.22</v>
@@ -20599,7 +20614,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20805,7 +20820,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20886,7 +20901,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ96">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR96">
         <v>1.65</v>
@@ -21089,10 +21104,10 @@
         <v>2.4</v>
       </c>
       <c r="AP97">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ97">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR97">
         <v>1.69</v>
@@ -21217,7 +21232,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21298,7 +21313,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ98">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR98">
         <v>1.06</v>
@@ -21501,7 +21516,7 @@
         <v>0.2</v>
       </c>
       <c r="AP99">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
         <v>0.11</v>
@@ -21707,7 +21722,7 @@
         <v>0.6</v>
       </c>
       <c r="AP100">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ100">
         <v>0.67</v>
@@ -22122,7 +22137,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ102">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR102">
         <v>1.45</v>
@@ -22247,7 +22262,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22325,10 +22340,10 @@
         <v>1.33</v>
       </c>
       <c r="AP103">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ103">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR103">
         <v>1.26</v>
@@ -22453,7 +22468,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22534,7 +22549,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ104">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR104">
         <v>1.78</v>
@@ -22740,7 +22755,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ105">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -22946,7 +22961,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ106">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR106">
         <v>1.41</v>
@@ -23149,7 +23164,7 @@
         <v>0.6</v>
       </c>
       <c r="AP107">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>0.78</v>
@@ -23277,7 +23292,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23355,7 +23370,7 @@
         <v>1.2</v>
       </c>
       <c r="AP108">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ108">
         <v>1.33</v>
@@ -23561,10 +23576,10 @@
         <v>1.4</v>
       </c>
       <c r="AP109">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ109">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR109">
         <v>1.6</v>
@@ -23973,7 +23988,7 @@
         <v>0.8</v>
       </c>
       <c r="AP111">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ111">
         <v>1</v>
@@ -24101,7 +24116,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24182,7 +24197,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ112">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -24385,7 +24400,7 @@
         <v>1.4</v>
       </c>
       <c r="AP113">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ113">
         <v>1.44</v>
@@ -24513,7 +24528,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24591,7 +24606,7 @@
         <v>0.67</v>
       </c>
       <c r="AP114">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ114">
         <v>1</v>
@@ -24800,7 +24815,7 @@
         <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR115">
         <v>1.51</v>
@@ -24925,7 +24940,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25209,10 +25224,10 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR117">
         <v>1.7</v>
@@ -25337,7 +25352,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25418,7 +25433,7 @@
         <v>0.1</v>
       </c>
       <c r="AQ118">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR118">
         <v>0.99</v>
@@ -25827,7 +25842,7 @@
         <v>1.5</v>
       </c>
       <c r="AP120">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ120">
         <v>1.33</v>
@@ -25955,7 +25970,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26036,7 +26051,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ121">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR121">
         <v>1.35</v>
@@ -26239,7 +26254,7 @@
         <v>0.5</v>
       </c>
       <c r="AP122">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ122">
         <v>0.67</v>
@@ -26860,7 +26875,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ125">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR125">
         <v>1.66</v>
@@ -27063,7 +27078,7 @@
         <v>0.17</v>
       </c>
       <c r="AP126">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ126">
         <v>0.11</v>
@@ -27269,10 +27284,10 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ127">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR127">
         <v>1.21</v>
@@ -27890,7 +27905,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ130">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28299,10 +28314,10 @@
         <v>1</v>
       </c>
       <c r="AP132">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ132">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR132">
         <v>1.26</v>
@@ -28508,7 +28523,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR133">
         <v>1.34</v>
@@ -28633,7 +28648,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28711,7 +28726,7 @@
         <v>0.43</v>
       </c>
       <c r="AP134">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.67</v>
@@ -28839,7 +28854,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -28917,10 +28932,10 @@
         <v>2</v>
       </c>
       <c r="AP135">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ135">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR135">
         <v>1.14</v>
@@ -29123,7 +29138,7 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29744,7 +29759,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ139">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR139">
         <v>1.46</v>
@@ -29869,7 +29884,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -29947,10 +29962,10 @@
         <v>1.13</v>
       </c>
       <c r="AP140">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AQ140">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.24</v>
@@ -30075,7 +30090,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30153,10 +30168,10 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ141">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR141">
         <v>1.72</v>
@@ -30362,7 +30377,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ142">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AR142">
         <v>1.78</v>
@@ -30565,7 +30580,7 @@
         <v>0.57</v>
       </c>
       <c r="AP143">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ143">
         <v>0.78</v>
@@ -30899,7 +30914,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -30977,10 +30992,10 @@
         <v>0.57</v>
       </c>
       <c r="AP145">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AQ145">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR145">
         <v>1.62</v>
@@ -31105,7 +31120,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31183,10 +31198,10 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ146">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR146">
         <v>1.08</v>
@@ -31311,7 +31326,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31389,7 +31404,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ147">
         <v>1.22</v>
@@ -31517,7 +31532,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31723,7 +31738,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31801,7 +31816,7 @@
         <v>0.88</v>
       </c>
       <c r="AP149">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ149">
         <v>1</v>
@@ -32135,7 +32150,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32216,7 +32231,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ151">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR151">
         <v>1.79</v>
@@ -32419,10 +32434,10 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ152">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32547,7 +32562,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32625,7 +32640,7 @@
         <v>1</v>
       </c>
       <c r="AP153">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
         <v>1</v>
@@ -32834,7 +32849,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR154">
         <v>1.27</v>
@@ -32959,7 +32974,7 @@
         <v>90</v>
       </c>
       <c r="P155" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="Q155">
         <v>4.5</v>
@@ -33371,7 +33386,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33577,7 +33592,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33783,7 +33798,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33989,7 +34004,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34764,6 +34779,1654 @@
       </c>
       <c r="BP163">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7469028</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F164">
+        <v>19</v>
+      </c>
+      <c r="G164" t="s">
+        <v>75</v>
+      </c>
+      <c r="H164" t="s">
+        <v>81</v>
+      </c>
+      <c r="I164">
+        <v>1</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>1</v>
+      </c>
+      <c r="L164">
+        <v>3</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>3</v>
+      </c>
+      <c r="O164" t="s">
+        <v>201</v>
+      </c>
+      <c r="P164" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q164">
+        <v>2.45</v>
+      </c>
+      <c r="R164">
+        <v>2.2</v>
+      </c>
+      <c r="S164">
+        <v>3.85</v>
+      </c>
+      <c r="T164">
+        <v>1.33</v>
+      </c>
+      <c r="U164">
+        <v>3</v>
+      </c>
+      <c r="V164">
+        <v>2.4</v>
+      </c>
+      <c r="W164">
+        <v>1.5</v>
+      </c>
+      <c r="X164">
+        <v>5.95</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>1.97</v>
+      </c>
+      <c r="AA164">
+        <v>3.65</v>
+      </c>
+      <c r="AB164">
+        <v>3.45</v>
+      </c>
+      <c r="AC164">
+        <v>1.04</v>
+      </c>
+      <c r="AD164">
+        <v>10</v>
+      </c>
+      <c r="AE164">
+        <v>1.22</v>
+      </c>
+      <c r="AF164">
+        <v>4.2</v>
+      </c>
+      <c r="AG164">
+        <v>1.65</v>
+      </c>
+      <c r="AH164">
+        <v>2.1</v>
+      </c>
+      <c r="AI164">
+        <v>1.55</v>
+      </c>
+      <c r="AJ164">
+        <v>2.25</v>
+      </c>
+      <c r="AK164">
+        <v>1.28</v>
+      </c>
+      <c r="AL164">
+        <v>1.22</v>
+      </c>
+      <c r="AM164">
+        <v>1.77</v>
+      </c>
+      <c r="AN164">
+        <v>1.89</v>
+      </c>
+      <c r="AO164">
+        <v>1.11</v>
+      </c>
+      <c r="AP164">
+        <v>2</v>
+      </c>
+      <c r="AQ164">
+        <v>1</v>
+      </c>
+      <c r="AR164">
+        <v>1.64</v>
+      </c>
+      <c r="AS164">
+        <v>1.29</v>
+      </c>
+      <c r="AT164">
+        <v>2.93</v>
+      </c>
+      <c r="AU164">
+        <v>6</v>
+      </c>
+      <c r="AV164">
+        <v>6</v>
+      </c>
+      <c r="AW164">
+        <v>7</v>
+      </c>
+      <c r="AX164">
+        <v>12</v>
+      </c>
+      <c r="AY164">
+        <v>13</v>
+      </c>
+      <c r="AZ164">
+        <v>18</v>
+      </c>
+      <c r="BA164">
+        <v>4</v>
+      </c>
+      <c r="BB164">
+        <v>9</v>
+      </c>
+      <c r="BC164">
+        <v>13</v>
+      </c>
+      <c r="BD164">
+        <v>1.7</v>
+      </c>
+      <c r="BE164">
+        <v>6.4</v>
+      </c>
+      <c r="BF164">
+        <v>2.4</v>
+      </c>
+      <c r="BG164">
+        <v>1.35</v>
+      </c>
+      <c r="BH164">
+        <v>2.88</v>
+      </c>
+      <c r="BI164">
+        <v>1.6</v>
+      </c>
+      <c r="BJ164">
+        <v>2.17</v>
+      </c>
+      <c r="BK164">
+        <v>1.98</v>
+      </c>
+      <c r="BL164">
+        <v>1.73</v>
+      </c>
+      <c r="BM164">
+        <v>2.5</v>
+      </c>
+      <c r="BN164">
+        <v>1.46</v>
+      </c>
+      <c r="BO164">
+        <v>3.3</v>
+      </c>
+      <c r="BP164">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7469029</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F165">
+        <v>19</v>
+      </c>
+      <c r="G165" t="s">
+        <v>74</v>
+      </c>
+      <c r="H165" t="s">
+        <v>77</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>1</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>1</v>
+      </c>
+      <c r="O165" t="s">
+        <v>202</v>
+      </c>
+      <c r="P165" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q165">
+        <v>2</v>
+      </c>
+      <c r="R165">
+        <v>2.3</v>
+      </c>
+      <c r="S165">
+        <v>5.5</v>
+      </c>
+      <c r="T165">
+        <v>1.33</v>
+      </c>
+      <c r="U165">
+        <v>3</v>
+      </c>
+      <c r="V165">
+        <v>2.55</v>
+      </c>
+      <c r="W165">
+        <v>1.45</v>
+      </c>
+      <c r="X165">
+        <v>6.55</v>
+      </c>
+      <c r="Y165">
+        <v>1.08</v>
+      </c>
+      <c r="Z165">
+        <v>1.53</v>
+      </c>
+      <c r="AA165">
+        <v>4.1</v>
+      </c>
+      <c r="AB165">
+        <v>5.8</v>
+      </c>
+      <c r="AC165">
+        <v>1.04</v>
+      </c>
+      <c r="AD165">
+        <v>10</v>
+      </c>
+      <c r="AE165">
+        <v>1.25</v>
+      </c>
+      <c r="AF165">
+        <v>3.85</v>
+      </c>
+      <c r="AG165">
+        <v>1.85</v>
+      </c>
+      <c r="AH165">
+        <v>1.89</v>
+      </c>
+      <c r="AI165">
+        <v>1.85</v>
+      </c>
+      <c r="AJ165">
+        <v>1.83</v>
+      </c>
+      <c r="AK165">
+        <v>1.12</v>
+      </c>
+      <c r="AL165">
+        <v>1.17</v>
+      </c>
+      <c r="AM165">
+        <v>2.5</v>
+      </c>
+      <c r="AN165">
+        <v>1.89</v>
+      </c>
+      <c r="AO165">
+        <v>1.38</v>
+      </c>
+      <c r="AP165">
+        <v>2</v>
+      </c>
+      <c r="AQ165">
+        <v>1.22</v>
+      </c>
+      <c r="AR165">
+        <v>1.13</v>
+      </c>
+      <c r="AS165">
+        <v>1.09</v>
+      </c>
+      <c r="AT165">
+        <v>2.22</v>
+      </c>
+      <c r="AU165">
+        <v>6</v>
+      </c>
+      <c r="AV165">
+        <v>4</v>
+      </c>
+      <c r="AW165">
+        <v>7</v>
+      </c>
+      <c r="AX165">
+        <v>8</v>
+      </c>
+      <c r="AY165">
+        <v>13</v>
+      </c>
+      <c r="AZ165">
+        <v>12</v>
+      </c>
+      <c r="BA165">
+        <v>5</v>
+      </c>
+      <c r="BB165">
+        <v>6</v>
+      </c>
+      <c r="BC165">
+        <v>11</v>
+      </c>
+      <c r="BD165">
+        <v>1.43</v>
+      </c>
+      <c r="BE165">
+        <v>6.75</v>
+      </c>
+      <c r="BF165">
+        <v>3.15</v>
+      </c>
+      <c r="BG165">
+        <v>1.43</v>
+      </c>
+      <c r="BH165">
+        <v>2.6</v>
+      </c>
+      <c r="BI165">
+        <v>1.73</v>
+      </c>
+      <c r="BJ165">
+        <v>1.98</v>
+      </c>
+      <c r="BK165">
+        <v>2.15</v>
+      </c>
+      <c r="BL165">
+        <v>1.61</v>
+      </c>
+      <c r="BM165">
+        <v>2.8</v>
+      </c>
+      <c r="BN165">
+        <v>1.38</v>
+      </c>
+      <c r="BO165">
+        <v>3.65</v>
+      </c>
+      <c r="BP165">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7469030</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F166">
+        <v>19</v>
+      </c>
+      <c r="G166" t="s">
+        <v>73</v>
+      </c>
+      <c r="H166" t="s">
+        <v>83</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>1</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>1</v>
+      </c>
+      <c r="O166" t="s">
+        <v>203</v>
+      </c>
+      <c r="P166" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q166">
+        <v>3.65</v>
+      </c>
+      <c r="R166">
+        <v>1.85</v>
+      </c>
+      <c r="S166">
+        <v>3.2</v>
+      </c>
+      <c r="T166">
+        <v>1.53</v>
+      </c>
+      <c r="U166">
+        <v>2.35</v>
+      </c>
+      <c r="V166">
+        <v>3.4</v>
+      </c>
+      <c r="W166">
+        <v>1.28</v>
+      </c>
+      <c r="X166">
+        <v>10.25</v>
+      </c>
+      <c r="Y166">
+        <v>1.02</v>
+      </c>
+      <c r="Z166">
+        <v>2.95</v>
+      </c>
+      <c r="AA166">
+        <v>3</v>
+      </c>
+      <c r="AB166">
+        <v>2.49</v>
+      </c>
+      <c r="AC166">
+        <v>1.1</v>
+      </c>
+      <c r="AD166">
+        <v>6.5</v>
+      </c>
+      <c r="AE166">
+        <v>1.48</v>
+      </c>
+      <c r="AF166">
+        <v>2.62</v>
+      </c>
+      <c r="AG166">
+        <v>2.3</v>
+      </c>
+      <c r="AH166">
+        <v>1.55</v>
+      </c>
+      <c r="AI166">
+        <v>1.95</v>
+      </c>
+      <c r="AJ166">
+        <v>1.73</v>
+      </c>
+      <c r="AK166">
+        <v>1.5</v>
+      </c>
+      <c r="AL166">
+        <v>1.3</v>
+      </c>
+      <c r="AM166">
+        <v>1.38</v>
+      </c>
+      <c r="AN166">
+        <v>1.89</v>
+      </c>
+      <c r="AO166">
+        <v>0.89</v>
+      </c>
+      <c r="AP166">
+        <v>2</v>
+      </c>
+      <c r="AQ166">
+        <v>0.8</v>
+      </c>
+      <c r="AR166">
+        <v>1.68</v>
+      </c>
+      <c r="AS166">
+        <v>1.35</v>
+      </c>
+      <c r="AT166">
+        <v>3.03</v>
+      </c>
+      <c r="AU166">
+        <v>3</v>
+      </c>
+      <c r="AV166">
+        <v>4</v>
+      </c>
+      <c r="AW166">
+        <v>5</v>
+      </c>
+      <c r="AX166">
+        <v>14</v>
+      </c>
+      <c r="AY166">
+        <v>8</v>
+      </c>
+      <c r="AZ166">
+        <v>18</v>
+      </c>
+      <c r="BA166">
+        <v>0</v>
+      </c>
+      <c r="BB166">
+        <v>1</v>
+      </c>
+      <c r="BC166">
+        <v>1</v>
+      </c>
+      <c r="BD166">
+        <v>2.15</v>
+      </c>
+      <c r="BE166">
+        <v>6.75</v>
+      </c>
+      <c r="BF166">
+        <v>1.88</v>
+      </c>
+      <c r="BG166">
+        <v>1.36</v>
+      </c>
+      <c r="BH166">
+        <v>2.8</v>
+      </c>
+      <c r="BI166">
+        <v>1.61</v>
+      </c>
+      <c r="BJ166">
+        <v>2.15</v>
+      </c>
+      <c r="BK166">
+        <v>1.98</v>
+      </c>
+      <c r="BL166">
+        <v>1.74</v>
+      </c>
+      <c r="BM166">
+        <v>2.48</v>
+      </c>
+      <c r="BN166">
+        <v>1.47</v>
+      </c>
+      <c r="BO166">
+        <v>3.2</v>
+      </c>
+      <c r="BP166">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7469032</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F167">
+        <v>19</v>
+      </c>
+      <c r="G167" t="s">
+        <v>87</v>
+      </c>
+      <c r="H167" t="s">
+        <v>82</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>2</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>3</v>
+      </c>
+      <c r="N167">
+        <v>4</v>
+      </c>
+      <c r="O167" t="s">
+        <v>109</v>
+      </c>
+      <c r="P167" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q167">
+        <v>3.35</v>
+      </c>
+      <c r="R167">
+        <v>2.05</v>
+      </c>
+      <c r="S167">
+        <v>3</v>
+      </c>
+      <c r="T167">
+        <v>1.4</v>
+      </c>
+      <c r="U167">
+        <v>2.75</v>
+      </c>
+      <c r="V167">
+        <v>2.75</v>
+      </c>
+      <c r="W167">
+        <v>1.4</v>
+      </c>
+      <c r="X167">
+        <v>7.1</v>
+      </c>
+      <c r="Y167">
+        <v>1.06</v>
+      </c>
+      <c r="Z167">
+        <v>2.8</v>
+      </c>
+      <c r="AA167">
+        <v>3.25</v>
+      </c>
+      <c r="AB167">
+        <v>2.47</v>
+      </c>
+      <c r="AC167">
+        <v>1.06</v>
+      </c>
+      <c r="AD167">
+        <v>8.5</v>
+      </c>
+      <c r="AE167">
+        <v>1.3</v>
+      </c>
+      <c r="AF167">
+        <v>3.4</v>
+      </c>
+      <c r="AG167">
+        <v>1.89</v>
+      </c>
+      <c r="AH167">
+        <v>1.85</v>
+      </c>
+      <c r="AI167">
+        <v>1.67</v>
+      </c>
+      <c r="AJ167">
+        <v>2.05</v>
+      </c>
+      <c r="AK167">
+        <v>1.53</v>
+      </c>
+      <c r="AL167">
+        <v>1.28</v>
+      </c>
+      <c r="AM167">
+        <v>1.42</v>
+      </c>
+      <c r="AN167">
+        <v>1.38</v>
+      </c>
+      <c r="AO167">
+        <v>0.67</v>
+      </c>
+      <c r="AP167">
+        <v>1.22</v>
+      </c>
+      <c r="AQ167">
+        <v>0.9</v>
+      </c>
+      <c r="AR167">
+        <v>1.14</v>
+      </c>
+      <c r="AS167">
+        <v>1.38</v>
+      </c>
+      <c r="AT167">
+        <v>2.52</v>
+      </c>
+      <c r="AU167">
+        <v>7</v>
+      </c>
+      <c r="AV167">
+        <v>10</v>
+      </c>
+      <c r="AW167">
+        <v>14</v>
+      </c>
+      <c r="AX167">
+        <v>9</v>
+      </c>
+      <c r="AY167">
+        <v>21</v>
+      </c>
+      <c r="AZ167">
+        <v>19</v>
+      </c>
+      <c r="BA167">
+        <v>7</v>
+      </c>
+      <c r="BB167">
+        <v>5</v>
+      </c>
+      <c r="BC167">
+        <v>12</v>
+      </c>
+      <c r="BD167">
+        <v>2.43</v>
+      </c>
+      <c r="BE167">
+        <v>6.4</v>
+      </c>
+      <c r="BF167">
+        <v>1.7</v>
+      </c>
+      <c r="BG167">
+        <v>1.28</v>
+      </c>
+      <c r="BH167">
+        <v>3.2</v>
+      </c>
+      <c r="BI167">
+        <v>1.5</v>
+      </c>
+      <c r="BJ167">
+        <v>2.38</v>
+      </c>
+      <c r="BK167">
+        <v>1.8</v>
+      </c>
+      <c r="BL167">
+        <v>1.89</v>
+      </c>
+      <c r="BM167">
+        <v>2.25</v>
+      </c>
+      <c r="BN167">
+        <v>1.55</v>
+      </c>
+      <c r="BO167">
+        <v>2.9</v>
+      </c>
+      <c r="BP167">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7469036</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45674.66666666666</v>
+      </c>
+      <c r="F168">
+        <v>19</v>
+      </c>
+      <c r="G168" t="s">
+        <v>71</v>
+      </c>
+      <c r="H168" t="s">
+        <v>76</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>2</v>
+      </c>
+      <c r="M168">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>3</v>
+      </c>
+      <c r="O168" t="s">
+        <v>204</v>
+      </c>
+      <c r="P168" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q168">
+        <v>3.45</v>
+      </c>
+      <c r="R168">
+        <v>1.91</v>
+      </c>
+      <c r="S168">
+        <v>3.25</v>
+      </c>
+      <c r="T168">
+        <v>1.5</v>
+      </c>
+      <c r="U168">
+        <v>2.4</v>
+      </c>
+      <c r="V168">
+        <v>3.25</v>
+      </c>
+      <c r="W168">
+        <v>1.3</v>
+      </c>
+      <c r="X168">
+        <v>10.25</v>
+      </c>
+      <c r="Y168">
+        <v>1.02</v>
+      </c>
+      <c r="Z168">
+        <v>2.9</v>
+      </c>
+      <c r="AA168">
+        <v>3.05</v>
+      </c>
+      <c r="AB168">
+        <v>2.55</v>
+      </c>
+      <c r="AC168">
+        <v>1.1</v>
+      </c>
+      <c r="AD168">
+        <v>6.5</v>
+      </c>
+      <c r="AE168">
+        <v>1.45</v>
+      </c>
+      <c r="AF168">
+        <v>2.7</v>
+      </c>
+      <c r="AG168">
+        <v>2.25</v>
+      </c>
+      <c r="AH168">
+        <v>1.57</v>
+      </c>
+      <c r="AI168">
+        <v>1.91</v>
+      </c>
+      <c r="AJ168">
+        <v>1.77</v>
+      </c>
+      <c r="AK168">
+        <v>1.48</v>
+      </c>
+      <c r="AL168">
+        <v>1.33</v>
+      </c>
+      <c r="AM168">
+        <v>1.4</v>
+      </c>
+      <c r="AN168">
+        <v>1.56</v>
+      </c>
+      <c r="AO168">
+        <v>0.5</v>
+      </c>
+      <c r="AP168">
+        <v>1.7</v>
+      </c>
+      <c r="AQ168">
+        <v>0.44</v>
+      </c>
+      <c r="AR168">
+        <v>1.22</v>
+      </c>
+      <c r="AS168">
+        <v>1.32</v>
+      </c>
+      <c r="AT168">
+        <v>2.54</v>
+      </c>
+      <c r="AU168">
+        <v>5</v>
+      </c>
+      <c r="AV168">
+        <v>4</v>
+      </c>
+      <c r="AW168">
+        <v>12</v>
+      </c>
+      <c r="AX168">
+        <v>2</v>
+      </c>
+      <c r="AY168">
+        <v>17</v>
+      </c>
+      <c r="AZ168">
+        <v>6</v>
+      </c>
+      <c r="BA168">
+        <v>10</v>
+      </c>
+      <c r="BB168">
+        <v>1</v>
+      </c>
+      <c r="BC168">
+        <v>11</v>
+      </c>
+      <c r="BD168">
+        <v>2.05</v>
+      </c>
+      <c r="BE168">
+        <v>6.1</v>
+      </c>
+      <c r="BF168">
+        <v>1.98</v>
+      </c>
+      <c r="BG168">
+        <v>1.49</v>
+      </c>
+      <c r="BH168">
+        <v>2.4</v>
+      </c>
+      <c r="BI168">
+        <v>1.82</v>
+      </c>
+      <c r="BJ168">
+        <v>1.86</v>
+      </c>
+      <c r="BK168">
+        <v>2.32</v>
+      </c>
+      <c r="BL168">
+        <v>1.53</v>
+      </c>
+      <c r="BM168">
+        <v>3.05</v>
+      </c>
+      <c r="BN168">
+        <v>1.32</v>
+      </c>
+      <c r="BO168">
+        <v>4</v>
+      </c>
+      <c r="BP168">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7469033</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45675.41666666666</v>
+      </c>
+      <c r="F169">
+        <v>19</v>
+      </c>
+      <c r="G169" t="s">
+        <v>70</v>
+      </c>
+      <c r="H169" t="s">
+        <v>80</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>2</v>
+      </c>
+      <c r="O169" t="s">
+        <v>205</v>
+      </c>
+      <c r="P169" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q169">
+        <v>2.8</v>
+      </c>
+      <c r="R169">
+        <v>2.05</v>
+      </c>
+      <c r="S169">
+        <v>3.75</v>
+      </c>
+      <c r="T169">
+        <v>1.41</v>
+      </c>
+      <c r="U169">
+        <v>2.7</v>
+      </c>
+      <c r="V169">
+        <v>2.95</v>
+      </c>
+      <c r="W169">
+        <v>1.35</v>
+      </c>
+      <c r="X169">
+        <v>7.4</v>
+      </c>
+      <c r="Y169">
+        <v>1.06</v>
+      </c>
+      <c r="Z169">
+        <v>2.18</v>
+      </c>
+      <c r="AA169">
+        <v>3.06</v>
+      </c>
+      <c r="AB169">
+        <v>3.15</v>
+      </c>
+      <c r="AC169">
+        <v>1.07</v>
+      </c>
+      <c r="AD169">
+        <v>8</v>
+      </c>
+      <c r="AE169">
+        <v>1.33</v>
+      </c>
+      <c r="AF169">
+        <v>3.2</v>
+      </c>
+      <c r="AG169">
+        <v>1.9</v>
+      </c>
+      <c r="AH169">
+        <v>1.8</v>
+      </c>
+      <c r="AI169">
+        <v>1.8</v>
+      </c>
+      <c r="AJ169">
+        <v>1.95</v>
+      </c>
+      <c r="AK169">
+        <v>1.33</v>
+      </c>
+      <c r="AL169">
+        <v>1.25</v>
+      </c>
+      <c r="AM169">
+        <v>1.68</v>
+      </c>
+      <c r="AN169">
+        <v>1.11</v>
+      </c>
+      <c r="AO169">
+        <v>1.56</v>
+      </c>
+      <c r="AP169">
+        <v>1.1</v>
+      </c>
+      <c r="AQ169">
+        <v>1.5</v>
+      </c>
+      <c r="AR169">
+        <v>1.32</v>
+      </c>
+      <c r="AS169">
+        <v>1.09</v>
+      </c>
+      <c r="AT169">
+        <v>2.41</v>
+      </c>
+      <c r="AU169">
+        <v>6</v>
+      </c>
+      <c r="AV169">
+        <v>2</v>
+      </c>
+      <c r="AW169">
+        <v>4</v>
+      </c>
+      <c r="AX169">
+        <v>8</v>
+      </c>
+      <c r="AY169">
+        <v>10</v>
+      </c>
+      <c r="AZ169">
+        <v>10</v>
+      </c>
+      <c r="BA169">
+        <v>4</v>
+      </c>
+      <c r="BB169">
+        <v>4</v>
+      </c>
+      <c r="BC169">
+        <v>8</v>
+      </c>
+      <c r="BD169">
+        <v>1.72</v>
+      </c>
+      <c r="BE169">
+        <v>6.75</v>
+      </c>
+      <c r="BF169">
+        <v>2.33</v>
+      </c>
+      <c r="BG169">
+        <v>1.28</v>
+      </c>
+      <c r="BH169">
+        <v>3.2</v>
+      </c>
+      <c r="BI169">
+        <v>1.49</v>
+      </c>
+      <c r="BJ169">
+        <v>2.4</v>
+      </c>
+      <c r="BK169">
+        <v>1.8</v>
+      </c>
+      <c r="BL169">
+        <v>1.89</v>
+      </c>
+      <c r="BM169">
+        <v>2.23</v>
+      </c>
+      <c r="BN169">
+        <v>1.56</v>
+      </c>
+      <c r="BO169">
+        <v>2.9</v>
+      </c>
+      <c r="BP169">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7469034</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45675.41666666666</v>
+      </c>
+      <c r="F170">
+        <v>19</v>
+      </c>
+      <c r="G170" t="s">
+        <v>78</v>
+      </c>
+      <c r="H170" t="s">
+        <v>85</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>1</v>
+      </c>
+      <c r="K170">
+        <v>2</v>
+      </c>
+      <c r="L170">
+        <v>3</v>
+      </c>
+      <c r="M170">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>4</v>
+      </c>
+      <c r="O170" t="s">
+        <v>206</v>
+      </c>
+      <c r="P170" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q170">
+        <v>3</v>
+      </c>
+      <c r="R170">
+        <v>1.95</v>
+      </c>
+      <c r="S170">
+        <v>3.6</v>
+      </c>
+      <c r="T170">
+        <v>1.48</v>
+      </c>
+      <c r="U170">
+        <v>2.45</v>
+      </c>
+      <c r="V170">
+        <v>3.2</v>
+      </c>
+      <c r="W170">
+        <v>1.3</v>
+      </c>
+      <c r="X170">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y170">
+        <v>1.03</v>
+      </c>
+      <c r="Z170">
+        <v>2.44</v>
+      </c>
+      <c r="AA170">
+        <v>3.03</v>
+      </c>
+      <c r="AB170">
+        <v>2.76</v>
+      </c>
+      <c r="AC170">
+        <v>1.09</v>
+      </c>
+      <c r="AD170">
+        <v>7</v>
+      </c>
+      <c r="AE170">
+        <v>1.42</v>
+      </c>
+      <c r="AF170">
+        <v>2.8</v>
+      </c>
+      <c r="AG170">
+        <v>2.11</v>
+      </c>
+      <c r="AH170">
+        <v>1.65</v>
+      </c>
+      <c r="AI170">
+        <v>1.85</v>
+      </c>
+      <c r="AJ170">
+        <v>1.83</v>
+      </c>
+      <c r="AK170">
+        <v>1.36</v>
+      </c>
+      <c r="AL170">
+        <v>1.3</v>
+      </c>
+      <c r="AM170">
+        <v>1.53</v>
+      </c>
+      <c r="AN170">
+        <v>2.11</v>
+      </c>
+      <c r="AO170">
+        <v>1.89</v>
+      </c>
+      <c r="AP170">
+        <v>2.2</v>
+      </c>
+      <c r="AQ170">
+        <v>1.7</v>
+      </c>
+      <c r="AR170">
+        <v>1.64</v>
+      </c>
+      <c r="AS170">
+        <v>1.42</v>
+      </c>
+      <c r="AT170">
+        <v>3.06</v>
+      </c>
+      <c r="AU170">
+        <v>7</v>
+      </c>
+      <c r="AV170">
+        <v>7</v>
+      </c>
+      <c r="AW170">
+        <v>2</v>
+      </c>
+      <c r="AX170">
+        <v>5</v>
+      </c>
+      <c r="AY170">
+        <v>9</v>
+      </c>
+      <c r="AZ170">
+        <v>12</v>
+      </c>
+      <c r="BA170">
+        <v>4</v>
+      </c>
+      <c r="BB170">
+        <v>7</v>
+      </c>
+      <c r="BC170">
+        <v>11</v>
+      </c>
+      <c r="BD170">
+        <v>1.84</v>
+      </c>
+      <c r="BE170">
+        <v>6.4</v>
+      </c>
+      <c r="BF170">
+        <v>2.17</v>
+      </c>
+      <c r="BG170">
+        <v>1.45</v>
+      </c>
+      <c r="BH170">
+        <v>2.55</v>
+      </c>
+      <c r="BI170">
+        <v>1.75</v>
+      </c>
+      <c r="BJ170">
+        <v>1.95</v>
+      </c>
+      <c r="BK170">
+        <v>2.2</v>
+      </c>
+      <c r="BL170">
+        <v>1.58</v>
+      </c>
+      <c r="BM170">
+        <v>2.9</v>
+      </c>
+      <c r="BN170">
+        <v>1.35</v>
+      </c>
+      <c r="BO170">
+        <v>3.8</v>
+      </c>
+      <c r="BP170">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7469031</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45675.66666666666</v>
+      </c>
+      <c r="F171">
+        <v>19</v>
+      </c>
+      <c r="G171" t="s">
+        <v>72</v>
+      </c>
+      <c r="H171" t="s">
+        <v>86</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>1</v>
+      </c>
+      <c r="O171" t="s">
+        <v>90</v>
+      </c>
+      <c r="P171" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q171">
+        <v>3.75</v>
+      </c>
+      <c r="R171">
+        <v>2</v>
+      </c>
+      <c r="S171">
+        <v>2.85</v>
+      </c>
+      <c r="T171">
+        <v>1.46</v>
+      </c>
+      <c r="U171">
+        <v>2.55</v>
+      </c>
+      <c r="V171">
+        <v>2.95</v>
+      </c>
+      <c r="W171">
+        <v>1.35</v>
+      </c>
+      <c r="X171">
+        <v>7.4</v>
+      </c>
+      <c r="Y171">
+        <v>1.06</v>
+      </c>
+      <c r="Z171">
+        <v>2.9</v>
+      </c>
+      <c r="AA171">
+        <v>2.9</v>
+      </c>
+      <c r="AB171">
+        <v>2.5</v>
+      </c>
+      <c r="AC171">
+        <v>1.07</v>
+      </c>
+      <c r="AD171">
+        <v>8</v>
+      </c>
+      <c r="AE171">
+        <v>1.33</v>
+      </c>
+      <c r="AF171">
+        <v>3.2</v>
+      </c>
+      <c r="AG171">
+        <v>1.85</v>
+      </c>
+      <c r="AH171">
+        <v>1.87</v>
+      </c>
+      <c r="AI171">
+        <v>1.78</v>
+      </c>
+      <c r="AJ171">
+        <v>1.95</v>
+      </c>
+      <c r="AK171">
+        <v>1.66</v>
+      </c>
+      <c r="AL171">
+        <v>1.3</v>
+      </c>
+      <c r="AM171">
+        <v>1.3</v>
+      </c>
+      <c r="AN171">
+        <v>2.67</v>
+      </c>
+      <c r="AO171">
+        <v>1</v>
+      </c>
+      <c r="AP171">
+        <v>2.4</v>
+      </c>
+      <c r="AQ171">
+        <v>1.2</v>
+      </c>
+      <c r="AR171">
+        <v>1.68</v>
+      </c>
+      <c r="AS171">
+        <v>1.48</v>
+      </c>
+      <c r="AT171">
+        <v>3.16</v>
+      </c>
+      <c r="AU171">
+        <v>3</v>
+      </c>
+      <c r="AV171">
+        <v>6</v>
+      </c>
+      <c r="AW171">
+        <v>5</v>
+      </c>
+      <c r="AX171">
+        <v>8</v>
+      </c>
+      <c r="AY171">
+        <v>8</v>
+      </c>
+      <c r="AZ171">
+        <v>14</v>
+      </c>
+      <c r="BA171">
+        <v>3</v>
+      </c>
+      <c r="BB171">
+        <v>7</v>
+      </c>
+      <c r="BC171">
+        <v>10</v>
+      </c>
+      <c r="BD171">
+        <v>2.38</v>
+      </c>
+      <c r="BE171">
+        <v>6.4</v>
+      </c>
+      <c r="BF171">
+        <v>1.73</v>
+      </c>
+      <c r="BG171">
+        <v>1.4</v>
+      </c>
+      <c r="BH171">
+        <v>2.65</v>
+      </c>
+      <c r="BI171">
+        <v>1.68</v>
+      </c>
+      <c r="BJ171">
+        <v>2.02</v>
+      </c>
+      <c r="BK171">
+        <v>2.08</v>
+      </c>
+      <c r="BL171">
+        <v>1.65</v>
+      </c>
+      <c r="BM171">
+        <v>2.65</v>
+      </c>
+      <c r="BN171">
+        <v>1.41</v>
+      </c>
+      <c r="BO171">
+        <v>3.45</v>
+      </c>
+      <c r="BP171">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1200,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1949,7 +1949,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ11">
         <v>1.44</v>
@@ -6069,7 +6069,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ24">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR24">
         <v>1.39</v>
@@ -8950,7 +8950,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ38">
         <v>1</v>
@@ -9571,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="AQ41">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR41">
         <v>1.73</v>
@@ -13279,7 +13279,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ59">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR59">
         <v>1.53</v>
@@ -14100,7 +14100,7 @@
         <v>3</v>
       </c>
       <c r="AP63">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ63">
         <v>1.33</v>
@@ -17605,7 +17605,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ80">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR80">
         <v>2.09</v>
@@ -17808,7 +17808,7 @@
         <v>2.25</v>
       </c>
       <c r="AP81">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ81">
         <v>1.7</v>
@@ -19868,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="AP91">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ91">
         <v>0.9</v>
@@ -20489,7 +20489,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR94">
         <v>1.21</v>
@@ -22134,7 +22134,7 @@
         <v>1.17</v>
       </c>
       <c r="AP102">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ102">
         <v>1.5</v>
@@ -23785,7 +23785,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ110">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR110">
         <v>1.85</v>
@@ -25636,7 +25636,7 @@
         <v>0.5</v>
       </c>
       <c r="AP119">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ119">
         <v>0.78</v>
@@ -26669,7 +26669,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ124">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR124">
         <v>1.79</v>
@@ -29756,7 +29756,7 @@
         <v>1.33</v>
       </c>
       <c r="AP139">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ139">
         <v>1.22</v>
@@ -31407,7 +31407,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AR147">
         <v>1.16</v>
@@ -36427,6 +36427,212 @@
       </c>
       <c r="BP171">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7469035</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45677.69791666666</v>
+      </c>
+      <c r="F172">
+        <v>19</v>
+      </c>
+      <c r="G172" t="s">
+        <v>79</v>
+      </c>
+      <c r="H172" t="s">
+        <v>84</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>1</v>
+      </c>
+      <c r="O172" t="s">
+        <v>90</v>
+      </c>
+      <c r="P172" t="s">
+        <v>220</v>
+      </c>
+      <c r="Q172">
+        <v>2.63</v>
+      </c>
+      <c r="R172">
+        <v>2.1</v>
+      </c>
+      <c r="S172">
+        <v>4.33</v>
+      </c>
+      <c r="T172">
+        <v>1.4</v>
+      </c>
+      <c r="U172">
+        <v>2.75</v>
+      </c>
+      <c r="V172">
+        <v>3</v>
+      </c>
+      <c r="W172">
+        <v>1.36</v>
+      </c>
+      <c r="X172">
+        <v>8</v>
+      </c>
+      <c r="Y172">
+        <v>1.08</v>
+      </c>
+      <c r="Z172">
+        <v>2</v>
+      </c>
+      <c r="AA172">
+        <v>3.25</v>
+      </c>
+      <c r="AB172">
+        <v>3.6</v>
+      </c>
+      <c r="AC172">
+        <v>1.06</v>
+      </c>
+      <c r="AD172">
+        <v>8.5</v>
+      </c>
+      <c r="AE172">
+        <v>1.33</v>
+      </c>
+      <c r="AF172">
+        <v>3.2</v>
+      </c>
+      <c r="AG172">
+        <v>2.03</v>
+      </c>
+      <c r="AH172">
+        <v>1.83</v>
+      </c>
+      <c r="AI172">
+        <v>1.8</v>
+      </c>
+      <c r="AJ172">
+        <v>1.91</v>
+      </c>
+      <c r="AK172">
+        <v>1.28</v>
+      </c>
+      <c r="AL172">
+        <v>1.25</v>
+      </c>
+      <c r="AM172">
+        <v>1.72</v>
+      </c>
+      <c r="AN172">
+        <v>1.38</v>
+      </c>
+      <c r="AO172">
+        <v>1.22</v>
+      </c>
+      <c r="AP172">
+        <v>1.22</v>
+      </c>
+      <c r="AQ172">
+        <v>1.4</v>
+      </c>
+      <c r="AR172">
+        <v>1.73</v>
+      </c>
+      <c r="AS172">
+        <v>1.3</v>
+      </c>
+      <c r="AT172">
+        <v>3.03</v>
+      </c>
+      <c r="AU172">
+        <v>5</v>
+      </c>
+      <c r="AV172">
+        <v>6</v>
+      </c>
+      <c r="AW172">
+        <v>10</v>
+      </c>
+      <c r="AX172">
+        <v>1</v>
+      </c>
+      <c r="AY172">
+        <v>22</v>
+      </c>
+      <c r="AZ172">
+        <v>8</v>
+      </c>
+      <c r="BA172">
+        <v>10</v>
+      </c>
+      <c r="BB172">
+        <v>3</v>
+      </c>
+      <c r="BC172">
+        <v>13</v>
+      </c>
+      <c r="BD172">
+        <v>1.65</v>
+      </c>
+      <c r="BE172">
+        <v>6.4</v>
+      </c>
+      <c r="BF172">
+        <v>2.48</v>
+      </c>
+      <c r="BG172">
+        <v>1.44</v>
+      </c>
+      <c r="BH172">
+        <v>2.55</v>
+      </c>
+      <c r="BI172">
+        <v>1.73</v>
+      </c>
+      <c r="BJ172">
+        <v>1.98</v>
+      </c>
+      <c r="BK172">
+        <v>2.17</v>
+      </c>
+      <c r="BL172">
+        <v>1.6</v>
+      </c>
+      <c r="BM172">
+        <v>2.8</v>
+      </c>
+      <c r="BN172">
+        <v>1.37</v>
+      </c>
+      <c r="BO172">
+        <v>3.7</v>
+      </c>
+      <c r="BP172">
+        <v>1.22</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -36575,13 +36575,13 @@
         <v>6</v>
       </c>
       <c r="AW172">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX172">
         <v>1</v>
       </c>
       <c r="AY172">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AZ172">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/France Ligue 2_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="280">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -637,6 +637,18 @@
     <t>['16', '55', '71']</t>
   </si>
   <si>
+    <t>['63']</t>
+  </si>
+  <si>
+    <t>['90+13']</t>
+  </si>
+  <si>
+    <t>['9', '24', '42']</t>
+  </si>
+  <si>
+    <t>['42', '56', '90+3']</t>
+  </si>
+  <si>
     <t>['16', '45+2']</t>
   </si>
   <si>
@@ -839,6 +851,9 @@
   </si>
   <si>
     <t>['20', '61', '70']</t>
+  </si>
+  <si>
+    <t>['26', '40']</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1456,7 +1471,7 @@
         <v>88</v>
       </c>
       <c r="P2" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q2">
         <v>2.4</v>
@@ -1537,7 +1552,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ2">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1868,7 +1883,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q4">
         <v>3.6</v>
@@ -2567,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="AQ7">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2692,7 +2707,7 @@
         <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q8">
         <v>3.1</v>
@@ -2770,7 +2785,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ8">
         <v>1.7</v>
@@ -2976,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ9">
         <v>1.2</v>
@@ -3104,7 +3119,7 @@
         <v>94</v>
       </c>
       <c r="P10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q10">
         <v>2.6</v>
@@ -3182,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10">
         <v>0.8</v>
@@ -3594,10 +3609,10 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ12">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3722,7 +3737,7 @@
         <v>95</v>
       </c>
       <c r="P13" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q13">
         <v>3.1</v>
@@ -3800,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ13">
         <v>1.33</v>
@@ -4212,10 +4227,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ15">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4340,7 +4355,7 @@
         <v>98</v>
       </c>
       <c r="P16" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q16">
         <v>2.63</v>
@@ -4546,7 +4561,7 @@
         <v>99</v>
       </c>
       <c r="P17" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -4833,7 +4848,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ18">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5039,7 +5054,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ19">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5245,7 +5260,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ20">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR20">
         <v>0.67</v>
@@ -5576,7 +5591,7 @@
         <v>103</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5988,7 +6003,7 @@
         <v>105</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6066,7 +6081,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ24">
         <v>1.4</v>
@@ -6272,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="AP25">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ25">
         <v>0.8</v>
@@ -6400,7 +6415,7 @@
         <v>106</v>
       </c>
       <c r="P26" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q26">
         <v>2.83</v>
@@ -6481,7 +6496,7 @@
         <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR26">
         <v>1.19</v>
@@ -6812,7 +6827,7 @@
         <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q28">
         <v>2.6</v>
@@ -6890,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ28">
         <v>1.5</v>
@@ -7096,10 +7111,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ29">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR29">
         <v>1.48</v>
@@ -7923,7 +7938,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ33">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR33">
         <v>2.15</v>
@@ -8126,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ34">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR34">
         <v>1.55</v>
@@ -8254,7 +8269,7 @@
         <v>113</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q35">
         <v>3.3</v>
@@ -8332,10 +8347,10 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ35">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR35">
         <v>1.69</v>
@@ -8460,7 +8475,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>3.1</v>
@@ -8666,7 +8681,7 @@
         <v>115</v>
       </c>
       <c r="P37" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q37">
         <v>3.4</v>
@@ -8872,7 +8887,7 @@
         <v>90</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>3.2</v>
@@ -9078,7 +9093,7 @@
         <v>90</v>
       </c>
       <c r="P39" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q39">
         <v>3.4</v>
@@ -9156,10 +9171,10 @@
         <v>0</v>
       </c>
       <c r="AP39">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ39">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR39">
         <v>0.8</v>
@@ -9362,7 +9377,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ40">
         <v>1.7</v>
@@ -9490,7 +9505,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>2.5</v>
@@ -9696,7 +9711,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>3.25</v>
@@ -9777,7 +9792,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ42">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR42">
         <v>1.75</v>
@@ -9902,7 +9917,7 @@
         <v>90</v>
       </c>
       <c r="P43" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q43">
         <v>2.75</v>
@@ -10186,10 +10201,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ44">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR44">
         <v>1.25</v>
@@ -10598,7 +10613,7 @@
         <v>1.5</v>
       </c>
       <c r="AP46">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ46">
         <v>1.2</v>
@@ -10804,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR47">
         <v>1.49</v>
@@ -11013,7 +11028,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR48">
         <v>1.82</v>
@@ -11216,7 +11231,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ49">
         <v>1.22</v>
@@ -11425,7 +11440,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR50">
         <v>1.61</v>
@@ -11837,7 +11852,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ52">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR52">
         <v>1.34</v>
@@ -11962,7 +11977,7 @@
         <v>128</v>
       </c>
       <c r="P53" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q53">
         <v>3.25</v>
@@ -12168,7 +12183,7 @@
         <v>129</v>
       </c>
       <c r="P54" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q54">
         <v>2.55</v>
@@ -12374,7 +12389,7 @@
         <v>130</v>
       </c>
       <c r="P55" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q55">
         <v>2.55</v>
@@ -12452,7 +12467,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ55">
         <v>1.5</v>
@@ -12661,7 +12676,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ56">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR56">
         <v>1.76</v>
@@ -12786,7 +12801,7 @@
         <v>132</v>
       </c>
       <c r="P57" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q57">
         <v>2.88</v>
@@ -12864,10 +12879,10 @@
         <v>0.67</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ57">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR57">
         <v>1.54</v>
@@ -12992,7 +13007,7 @@
         <v>133</v>
       </c>
       <c r="P58" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q58">
         <v>2.88</v>
@@ -13070,7 +13085,7 @@
         <v>1.5</v>
       </c>
       <c r="AP58">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ58">
         <v>1</v>
@@ -13198,7 +13213,7 @@
         <v>134</v>
       </c>
       <c r="P59" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q59">
         <v>2.62</v>
@@ -13276,7 +13291,7 @@
         <v>1.67</v>
       </c>
       <c r="AP59">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ59">
         <v>1.4</v>
@@ -13404,7 +13419,7 @@
         <v>135</v>
       </c>
       <c r="P60" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q60">
         <v>2.88</v>
@@ -13816,7 +13831,7 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q62">
         <v>3.6</v>
@@ -14022,7 +14037,7 @@
         <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>3.75</v>
@@ -14927,7 +14942,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ67">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR67">
         <v>1.61</v>
@@ -15052,7 +15067,7 @@
         <v>143</v>
       </c>
       <c r="P68" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15130,10 +15145,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ68">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR68">
         <v>1.95</v>
@@ -15258,7 +15273,7 @@
         <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q69">
         <v>2.5</v>
@@ -15464,7 +15479,7 @@
         <v>145</v>
       </c>
       <c r="P70" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q70">
         <v>3.75</v>
@@ -15542,7 +15557,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ70">
         <v>1.2</v>
@@ -15751,7 +15766,7 @@
         <v>1.1</v>
       </c>
       <c r="AQ71">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15876,7 +15891,7 @@
         <v>147</v>
       </c>
       <c r="P72" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q72">
         <v>2.2</v>
@@ -15954,10 +15969,10 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ72">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR72">
         <v>1.72</v>
@@ -16082,7 +16097,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q73">
         <v>4.33</v>
@@ -16160,7 +16175,7 @@
         <v>0.75</v>
       </c>
       <c r="AP73">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ73">
         <v>1</v>
@@ -16288,7 +16303,7 @@
         <v>90</v>
       </c>
       <c r="P74" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q74">
         <v>2.4</v>
@@ -16369,7 +16384,7 @@
         <v>2</v>
       </c>
       <c r="AQ74">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR74">
         <v>1.85</v>
@@ -16494,7 +16509,7 @@
         <v>148</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>3.5</v>
@@ -16700,7 +16715,7 @@
         <v>149</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.88</v>
@@ -16778,7 +16793,7 @@
         <v>1.33</v>
       </c>
       <c r="AP76">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17190,7 +17205,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ78">
         <v>1.44</v>
@@ -17318,7 +17333,7 @@
         <v>151</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q79">
         <v>3</v>
@@ -17399,7 +17414,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17524,7 +17539,7 @@
         <v>152</v>
       </c>
       <c r="P80" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q80">
         <v>2.05</v>
@@ -17730,7 +17745,7 @@
         <v>90</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>4.33</v>
@@ -18554,7 +18569,7 @@
         <v>90</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>3.1</v>
@@ -18635,7 +18650,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR85">
         <v>1.48</v>
@@ -18760,7 +18775,7 @@
         <v>156</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18838,7 +18853,7 @@
         <v>1.4</v>
       </c>
       <c r="AP86">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ86">
         <v>1.2</v>
@@ -19250,10 +19265,10 @@
         <v>1.5</v>
       </c>
       <c r="AP88">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR88">
         <v>1.77</v>
@@ -19459,7 +19474,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ89">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR89">
         <v>1.72</v>
@@ -19584,7 +19599,7 @@
         <v>90</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>2.38</v>
@@ -19662,10 +19677,10 @@
         <v>0.2</v>
       </c>
       <c r="AP90">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR90">
         <v>1.42</v>
@@ -19871,7 +19886,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ91">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR91">
         <v>1.25</v>
@@ -19996,7 +20011,7 @@
         <v>160</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20074,7 +20089,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ92">
         <v>1.44</v>
@@ -20614,7 +20629,7 @@
         <v>162</v>
       </c>
       <c r="P95" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>1.9</v>
@@ -20820,7 +20835,7 @@
         <v>163</v>
       </c>
       <c r="P96" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q96">
         <v>2.75</v>
@@ -20898,7 +20913,7 @@
         <v>1.2</v>
       </c>
       <c r="AP96">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ96">
         <v>1</v>
@@ -21232,7 +21247,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q98">
         <v>4.75</v>
@@ -21310,7 +21325,7 @@
         <v>0.25</v>
       </c>
       <c r="AP98">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ98">
         <v>0.44</v>
@@ -21519,7 +21534,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR99">
         <v>1.8</v>
@@ -21725,7 +21740,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ100">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR100">
         <v>1.57</v>
@@ -21928,7 +21943,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ101">
         <v>1.1</v>
@@ -22262,7 +22277,7 @@
         <v>166</v>
       </c>
       <c r="P103" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q103">
         <v>4.2</v>
@@ -22468,7 +22483,7 @@
         <v>167</v>
       </c>
       <c r="P104" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q104">
         <v>2.25</v>
@@ -22755,7 +22770,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ105">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR105">
         <v>1.41</v>
@@ -22958,7 +22973,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>0.8</v>
@@ -23167,7 +23182,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR107">
         <v>1.74</v>
@@ -23292,7 +23307,7 @@
         <v>90</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q108">
         <v>4.5</v>
@@ -23782,7 +23797,7 @@
         <v>1.17</v>
       </c>
       <c r="AP110">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ110">
         <v>1.4</v>
@@ -24116,7 +24131,7 @@
         <v>173</v>
       </c>
       <c r="P112" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q112">
         <v>3.5</v>
@@ -24194,7 +24209,7 @@
         <v>1</v>
       </c>
       <c r="AP112">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ112">
         <v>0.8</v>
@@ -24528,7 +24543,7 @@
         <v>90</v>
       </c>
       <c r="P114" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q114">
         <v>2.85</v>
@@ -24609,7 +24624,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR114">
         <v>1.28</v>
@@ -24940,7 +24955,7 @@
         <v>175</v>
       </c>
       <c r="P116" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25021,7 +25036,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ116">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR116">
         <v>1.94</v>
@@ -25224,7 +25239,7 @@
         <v>0.8</v>
       </c>
       <c r="AP117">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ117">
         <v>0.44</v>
@@ -25352,7 +25367,7 @@
         <v>90</v>
       </c>
       <c r="P118" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q118">
         <v>4</v>
@@ -25430,7 +25445,7 @@
         <v>1.14</v>
       </c>
       <c r="AP118">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ118">
         <v>1.5</v>
@@ -25639,7 +25654,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ119">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR119">
         <v>1.46</v>
@@ -25970,7 +25985,7 @@
         <v>178</v>
       </c>
       <c r="P121" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q121">
         <v>2.88</v>
@@ -26048,7 +26063,7 @@
         <v>1.14</v>
       </c>
       <c r="AP121">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26257,7 +26272,7 @@
         <v>2</v>
       </c>
       <c r="AQ122">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR122">
         <v>1.78</v>
@@ -26872,7 +26887,7 @@
         <v>1.14</v>
       </c>
       <c r="AP125">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ125">
         <v>1.2</v>
@@ -27081,7 +27096,7 @@
         <v>2.4</v>
       </c>
       <c r="AQ126">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR126">
         <v>1.58</v>
@@ -27493,7 +27508,7 @@
         <v>2.78</v>
       </c>
       <c r="AQ128">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR128">
         <v>1.83</v>
@@ -27696,10 +27711,10 @@
         <v>1</v>
       </c>
       <c r="AP129">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ129">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR129">
         <v>0.99</v>
@@ -27902,10 +27917,10 @@
         <v>0.71</v>
       </c>
       <c r="AP130">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ130">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR130">
         <v>1.89</v>
@@ -28520,7 +28535,7 @@
         <v>0.67</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ133">
         <v>0.44</v>
@@ -28648,7 +28663,7 @@
         <v>90</v>
       </c>
       <c r="P134" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q134">
         <v>3.2</v>
@@ -28729,7 +28744,7 @@
         <v>2</v>
       </c>
       <c r="AQ134">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR134">
         <v>1.08</v>
@@ -28854,7 +28869,7 @@
         <v>90</v>
       </c>
       <c r="P135" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q135">
         <v>5</v>
@@ -29138,7 +29153,7 @@
         <v>1.17</v>
       </c>
       <c r="AP136">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ136">
         <v>1</v>
@@ -29344,10 +29359,10 @@
         <v>1.29</v>
       </c>
       <c r="AP137">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ137">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR137">
         <v>1.66</v>
@@ -29553,7 +29568,7 @@
         <v>2</v>
       </c>
       <c r="AQ138">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR138">
         <v>1.44</v>
@@ -29884,7 +29899,7 @@
         <v>188</v>
       </c>
       <c r="P140" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q140">
         <v>2.95</v>
@@ -30090,7 +30105,7 @@
         <v>189</v>
       </c>
       <c r="P141" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>2.8</v>
@@ -30583,7 +30598,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ143">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR143">
         <v>1.16</v>
@@ -30914,7 +30929,7 @@
         <v>192</v>
       </c>
       <c r="P145" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q145">
         <v>2.75</v>
@@ -31120,7 +31135,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q146">
         <v>3.75</v>
@@ -31326,7 +31341,7 @@
         <v>129</v>
       </c>
       <c r="P147" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q147">
         <v>3.75</v>
@@ -31532,7 +31547,7 @@
         <v>90</v>
       </c>
       <c r="P148" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q148">
         <v>2.4</v>
@@ -31610,7 +31625,7 @@
         <v>0.88</v>
       </c>
       <c r="AP148">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ148">
         <v>1.1</v>
@@ -31738,7 +31753,7 @@
         <v>90</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31819,7 +31834,7 @@
         <v>2</v>
       </c>
       <c r="AQ149">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR149">
         <v>1.68</v>
@@ -32022,7 +32037,7 @@
         <v>1</v>
       </c>
       <c r="AP150">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ150">
         <v>1.44</v>
@@ -32150,7 +32165,7 @@
         <v>194</v>
       </c>
       <c r="P151" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q151">
         <v>1.62</v>
@@ -32434,10 +32449,10 @@
         <v>0.63</v>
       </c>
       <c r="AP152">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ152">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR152">
         <v>1.6</v>
@@ -32562,7 +32577,7 @@
         <v>95</v>
       </c>
       <c r="P153" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q153">
         <v>2.63</v>
@@ -32846,7 +32861,7 @@
         <v>1.13</v>
       </c>
       <c r="AP154">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ154">
         <v>1.2</v>
@@ -33052,7 +33067,7 @@
         <v>1.25</v>
       </c>
       <c r="AP155">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="AQ155">
         <v>1.44</v>
@@ -33386,7 +33401,7 @@
         <v>197</v>
       </c>
       <c r="P157" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q157">
         <v>2.7</v>
@@ -33464,10 +33479,10 @@
         <v>1.11</v>
       </c>
       <c r="AP157">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR157">
         <v>1.86</v>
@@ -33592,7 +33607,7 @@
         <v>96</v>
       </c>
       <c r="P158" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q158">
         <v>2.55</v>
@@ -33670,7 +33685,7 @@
         <v>1.11</v>
       </c>
       <c r="AP158">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ158">
         <v>1.1</v>
@@ -33798,7 +33813,7 @@
         <v>198</v>
       </c>
       <c r="P159" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q159">
         <v>3.3</v>
@@ -33879,7 +33894,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ159">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AR159">
         <v>1.45</v>
@@ -34004,7 +34019,7 @@
         <v>90</v>
       </c>
       <c r="P160" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q160">
         <v>2.75</v>
@@ -34082,10 +34097,10 @@
         <v>0.5</v>
       </c>
       <c r="AP160">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AQ160">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR160">
         <v>1.38</v>
@@ -34291,7 +34306,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ161">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR161">
         <v>1.88</v>
@@ -34494,10 +34509,10 @@
         <v>0.13</v>
       </c>
       <c r="AP162">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AQ162">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR162">
         <v>1.68</v>
@@ -35446,7 +35461,7 @@
         <v>109</v>
       </c>
       <c r="P167" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q167">
         <v>3.35</v>
@@ -35527,7 +35542,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ167">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AR167">
         <v>1.14</v>
@@ -35858,7 +35873,7 @@
         <v>205</v>
       </c>
       <c r="P169" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q169">
         <v>2.8</v>
@@ -36064,7 +36079,7 @@
         <v>206</v>
       </c>
       <c r="P170" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q170">
         <v>3</v>
@@ -36142,7 +36157,7 @@
         <v>1.89</v>
       </c>
       <c r="AP170">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ170">
         <v>1.7</v>
@@ -36476,7 +36491,7 @@
         <v>90</v>
       </c>
       <c r="P172" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q172">
         <v>2.63</v>
@@ -36633,6 +36648,1242 @@
       </c>
       <c r="BP172">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7469043</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F173">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s">
+        <v>71</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>2</v>
+      </c>
+      <c r="K173">
+        <v>2</v>
+      </c>
+      <c r="L173">
+        <v>1</v>
+      </c>
+      <c r="M173">
+        <v>2</v>
+      </c>
+      <c r="N173">
+        <v>3</v>
+      </c>
+      <c r="O173" t="s">
+        <v>207</v>
+      </c>
+      <c r="P173" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q173">
+        <v>2.3</v>
+      </c>
+      <c r="R173">
+        <v>2.15</v>
+      </c>
+      <c r="S173">
+        <v>4.5</v>
+      </c>
+      <c r="T173">
+        <v>1.38</v>
+      </c>
+      <c r="U173">
+        <v>2.8</v>
+      </c>
+      <c r="V173">
+        <v>2.75</v>
+      </c>
+      <c r="W173">
+        <v>1.4</v>
+      </c>
+      <c r="X173">
+        <v>7</v>
+      </c>
+      <c r="Y173">
+        <v>1.06</v>
+      </c>
+      <c r="Z173">
+        <v>1.73</v>
+      </c>
+      <c r="AA173">
+        <v>3.66</v>
+      </c>
+      <c r="AB173">
+        <v>4.6</v>
+      </c>
+      <c r="AC173">
+        <v>1.06</v>
+      </c>
+      <c r="AD173">
+        <v>8.5</v>
+      </c>
+      <c r="AE173">
+        <v>1.3</v>
+      </c>
+      <c r="AF173">
+        <v>3.35</v>
+      </c>
+      <c r="AG173">
+        <v>1.94</v>
+      </c>
+      <c r="AH173">
+        <v>1.8</v>
+      </c>
+      <c r="AI173">
+        <v>1.83</v>
+      </c>
+      <c r="AJ173">
+        <v>1.83</v>
+      </c>
+      <c r="AK173">
+        <v>1.18</v>
+      </c>
+      <c r="AL173">
+        <v>1.22</v>
+      </c>
+      <c r="AM173">
+        <v>2</v>
+      </c>
+      <c r="AN173">
+        <v>1.44</v>
+      </c>
+      <c r="AO173">
+        <v>0.11</v>
+      </c>
+      <c r="AP173">
+        <v>1.3</v>
+      </c>
+      <c r="AQ173">
+        <v>0.4</v>
+      </c>
+      <c r="AR173">
+        <v>1.78</v>
+      </c>
+      <c r="AS173">
+        <v>1.03</v>
+      </c>
+      <c r="AT173">
+        <v>2.81</v>
+      </c>
+      <c r="AU173">
+        <v>6</v>
+      </c>
+      <c r="AV173">
+        <v>3</v>
+      </c>
+      <c r="AW173">
+        <v>15</v>
+      </c>
+      <c r="AX173">
+        <v>3</v>
+      </c>
+      <c r="AY173">
+        <v>21</v>
+      </c>
+      <c r="AZ173">
+        <v>6</v>
+      </c>
+      <c r="BA173">
+        <v>11</v>
+      </c>
+      <c r="BB173">
+        <v>3</v>
+      </c>
+      <c r="BC173">
+        <v>14</v>
+      </c>
+      <c r="BD173">
+        <v>1.57</v>
+      </c>
+      <c r="BE173">
+        <v>6.4</v>
+      </c>
+      <c r="BF173">
+        <v>2.7</v>
+      </c>
+      <c r="BG173">
+        <v>1.45</v>
+      </c>
+      <c r="BH173">
+        <v>2.55</v>
+      </c>
+      <c r="BI173">
+        <v>1.74</v>
+      </c>
+      <c r="BJ173">
+        <v>1.97</v>
+      </c>
+      <c r="BK173">
+        <v>2.18</v>
+      </c>
+      <c r="BL173">
+        <v>1.58</v>
+      </c>
+      <c r="BM173">
+        <v>2.8</v>
+      </c>
+      <c r="BN173">
+        <v>1.38</v>
+      </c>
+      <c r="BO173">
+        <v>3.8</v>
+      </c>
+      <c r="BP173">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7469042</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F174">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>83</v>
+      </c>
+      <c r="H174" t="s">
+        <v>82</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>1</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>2</v>
+      </c>
+      <c r="O174" t="s">
+        <v>208</v>
+      </c>
+      <c r="P174" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q174">
+        <v>2.5</v>
+      </c>
+      <c r="R174">
+        <v>2.05</v>
+      </c>
+      <c r="S174">
+        <v>4.33</v>
+      </c>
+      <c r="T174">
+        <v>1.42</v>
+      </c>
+      <c r="U174">
+        <v>2.65</v>
+      </c>
+      <c r="V174">
+        <v>2.88</v>
+      </c>
+      <c r="W174">
+        <v>1.36</v>
+      </c>
+      <c r="X174">
+        <v>7.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.05</v>
+      </c>
+      <c r="Z174">
+        <v>1.93</v>
+      </c>
+      <c r="AA174">
+        <v>3.38</v>
+      </c>
+      <c r="AB174">
+        <v>3.9</v>
+      </c>
+      <c r="AC174">
+        <v>1.07</v>
+      </c>
+      <c r="AD174">
+        <v>8</v>
+      </c>
+      <c r="AE174">
+        <v>1.36</v>
+      </c>
+      <c r="AF174">
+        <v>3.1</v>
+      </c>
+      <c r="AG174">
+        <v>1.94</v>
+      </c>
+      <c r="AH174">
+        <v>1.76</v>
+      </c>
+      <c r="AI174">
+        <v>1.83</v>
+      </c>
+      <c r="AJ174">
+        <v>1.83</v>
+      </c>
+      <c r="AK174">
+        <v>1.22</v>
+      </c>
+      <c r="AL174">
+        <v>1.25</v>
+      </c>
+      <c r="AM174">
+        <v>1.83</v>
+      </c>
+      <c r="AN174">
+        <v>1.89</v>
+      </c>
+      <c r="AO174">
+        <v>0.9</v>
+      </c>
+      <c r="AP174">
+        <v>1.8</v>
+      </c>
+      <c r="AQ174">
+        <v>0.91</v>
+      </c>
+      <c r="AR174">
+        <v>1.67</v>
+      </c>
+      <c r="AS174">
+        <v>1.46</v>
+      </c>
+      <c r="AT174">
+        <v>3.13</v>
+      </c>
+      <c r="AU174">
+        <v>6</v>
+      </c>
+      <c r="AV174">
+        <v>6</v>
+      </c>
+      <c r="AW174">
+        <v>11</v>
+      </c>
+      <c r="AX174">
+        <v>2</v>
+      </c>
+      <c r="AY174">
+        <v>17</v>
+      </c>
+      <c r="AZ174">
+        <v>8</v>
+      </c>
+      <c r="BA174">
+        <v>8</v>
+      </c>
+      <c r="BB174">
+        <v>3</v>
+      </c>
+      <c r="BC174">
+        <v>11</v>
+      </c>
+      <c r="BD174">
+        <v>1.64</v>
+      </c>
+      <c r="BE174">
+        <v>6.25</v>
+      </c>
+      <c r="BF174">
+        <v>2.55</v>
+      </c>
+      <c r="BG174">
+        <v>1.46</v>
+      </c>
+      <c r="BH174">
+        <v>2.48</v>
+      </c>
+      <c r="BI174">
+        <v>1.77</v>
+      </c>
+      <c r="BJ174">
+        <v>1.93</v>
+      </c>
+      <c r="BK174">
+        <v>2.23</v>
+      </c>
+      <c r="BL174">
+        <v>1.56</v>
+      </c>
+      <c r="BM174">
+        <v>2.9</v>
+      </c>
+      <c r="BN174">
+        <v>1.34</v>
+      </c>
+      <c r="BO174">
+        <v>3.9</v>
+      </c>
+      <c r="BP174">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7469041</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F175">
+        <v>20</v>
+      </c>
+      <c r="G175" t="s">
+        <v>77</v>
+      </c>
+      <c r="H175" t="s">
+        <v>73</v>
+      </c>
+      <c r="I175">
+        <v>3</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>3</v>
+      </c>
+      <c r="L175">
+        <v>3</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>3</v>
+      </c>
+      <c r="O175" t="s">
+        <v>209</v>
+      </c>
+      <c r="P175" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q175">
+        <v>4.33</v>
+      </c>
+      <c r="R175">
+        <v>2.1</v>
+      </c>
+      <c r="S175">
+        <v>2.45</v>
+      </c>
+      <c r="T175">
+        <v>1.42</v>
+      </c>
+      <c r="U175">
+        <v>2.65</v>
+      </c>
+      <c r="V175">
+        <v>2.88</v>
+      </c>
+      <c r="W175">
+        <v>1.36</v>
+      </c>
+      <c r="X175">
+        <v>7.3</v>
+      </c>
+      <c r="Y175">
+        <v>1.06</v>
+      </c>
+      <c r="Z175">
+        <v>3.95</v>
+      </c>
+      <c r="AA175">
+        <v>3.5</v>
+      </c>
+      <c r="AB175">
+        <v>1.88</v>
+      </c>
+      <c r="AC175">
+        <v>1.06</v>
+      </c>
+      <c r="AD175">
+        <v>8.5</v>
+      </c>
+      <c r="AE175">
+        <v>1.36</v>
+      </c>
+      <c r="AF175">
+        <v>3.1</v>
+      </c>
+      <c r="AG175">
+        <v>1.98</v>
+      </c>
+      <c r="AH175">
+        <v>1.77</v>
+      </c>
+      <c r="AI175">
+        <v>1.83</v>
+      </c>
+      <c r="AJ175">
+        <v>1.83</v>
+      </c>
+      <c r="AK175">
+        <v>1.83</v>
+      </c>
+      <c r="AL175">
+        <v>1.25</v>
+      </c>
+      <c r="AM175">
+        <v>1.22</v>
+      </c>
+      <c r="AN175">
+        <v>0.1</v>
+      </c>
+      <c r="AO175">
+        <v>0.67</v>
+      </c>
+      <c r="AP175">
+        <v>0.36</v>
+      </c>
+      <c r="AQ175">
+        <v>0.6</v>
+      </c>
+      <c r="AR175">
+        <v>0.95</v>
+      </c>
+      <c r="AS175">
+        <v>1.27</v>
+      </c>
+      <c r="AT175">
+        <v>2.22</v>
+      </c>
+      <c r="AU175">
+        <v>6</v>
+      </c>
+      <c r="AV175">
+        <v>5</v>
+      </c>
+      <c r="AW175">
+        <v>8</v>
+      </c>
+      <c r="AX175">
+        <v>6</v>
+      </c>
+      <c r="AY175">
+        <v>14</v>
+      </c>
+      <c r="AZ175">
+        <v>11</v>
+      </c>
+      <c r="BA175">
+        <v>4</v>
+      </c>
+      <c r="BB175">
+        <v>3</v>
+      </c>
+      <c r="BC175">
+        <v>7</v>
+      </c>
+      <c r="BD175">
+        <v>2.55</v>
+      </c>
+      <c r="BE175">
+        <v>6.4</v>
+      </c>
+      <c r="BF175">
+        <v>1.63</v>
+      </c>
+      <c r="BG175">
+        <v>1.45</v>
+      </c>
+      <c r="BH175">
+        <v>2.55</v>
+      </c>
+      <c r="BI175">
+        <v>1.75</v>
+      </c>
+      <c r="BJ175">
+        <v>1.95</v>
+      </c>
+      <c r="BK175">
+        <v>2.2</v>
+      </c>
+      <c r="BL175">
+        <v>1.58</v>
+      </c>
+      <c r="BM175">
+        <v>2.85</v>
+      </c>
+      <c r="BN175">
+        <v>1.36</v>
+      </c>
+      <c r="BO175">
+        <v>3.8</v>
+      </c>
+      <c r="BP175">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7469039</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F176">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>80</v>
+      </c>
+      <c r="H176" t="s">
+        <v>79</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>1</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>1</v>
+      </c>
+      <c r="O176" t="s">
+        <v>105</v>
+      </c>
+      <c r="P176" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q176">
+        <v>3.25</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>3.4</v>
+      </c>
+      <c r="T176">
+        <v>1.44</v>
+      </c>
+      <c r="U176">
+        <v>2.63</v>
+      </c>
+      <c r="V176">
+        <v>3.25</v>
+      </c>
+      <c r="W176">
+        <v>1.33</v>
+      </c>
+      <c r="X176">
+        <v>9</v>
+      </c>
+      <c r="Y176">
+        <v>1.07</v>
+      </c>
+      <c r="Z176">
+        <v>2.38</v>
+      </c>
+      <c r="AA176">
+        <v>3.13</v>
+      </c>
+      <c r="AB176">
+        <v>3.02</v>
+      </c>
+      <c r="AC176">
+        <v>1.08</v>
+      </c>
+      <c r="AD176">
+        <v>7.5</v>
+      </c>
+      <c r="AE176">
+        <v>1.38</v>
+      </c>
+      <c r="AF176">
+        <v>2.9</v>
+      </c>
+      <c r="AG176">
+        <v>2.03</v>
+      </c>
+      <c r="AH176">
+        <v>1.72</v>
+      </c>
+      <c r="AI176">
+        <v>1.8</v>
+      </c>
+      <c r="AJ176">
+        <v>1.91</v>
+      </c>
+      <c r="AK176">
+        <v>1.36</v>
+      </c>
+      <c r="AL176">
+        <v>1.34</v>
+      </c>
+      <c r="AM176">
+        <v>1.55</v>
+      </c>
+      <c r="AN176">
+        <v>1.67</v>
+      </c>
+      <c r="AO176">
+        <v>1</v>
+      </c>
+      <c r="AP176">
+        <v>1.8</v>
+      </c>
+      <c r="AQ176">
+        <v>0.91</v>
+      </c>
+      <c r="AR176">
+        <v>1.28</v>
+      </c>
+      <c r="AS176">
+        <v>1.23</v>
+      </c>
+      <c r="AT176">
+        <v>2.51</v>
+      </c>
+      <c r="AU176">
+        <v>3</v>
+      </c>
+      <c r="AV176">
+        <v>2</v>
+      </c>
+      <c r="AW176">
+        <v>9</v>
+      </c>
+      <c r="AX176">
+        <v>17</v>
+      </c>
+      <c r="AY176">
+        <v>12</v>
+      </c>
+      <c r="AZ176">
+        <v>19</v>
+      </c>
+      <c r="BA176">
+        <v>3</v>
+      </c>
+      <c r="BB176">
+        <v>8</v>
+      </c>
+      <c r="BC176">
+        <v>11</v>
+      </c>
+      <c r="BD176">
+        <v>1.82</v>
+      </c>
+      <c r="BE176">
+        <v>8</v>
+      </c>
+      <c r="BF176">
+        <v>2.39</v>
+      </c>
+      <c r="BG176">
+        <v>1.32</v>
+      </c>
+      <c r="BH176">
+        <v>3.22</v>
+      </c>
+      <c r="BI176">
+        <v>1.56</v>
+      </c>
+      <c r="BJ176">
+        <v>2.33</v>
+      </c>
+      <c r="BK176">
+        <v>2</v>
+      </c>
+      <c r="BL176">
+        <v>1.8</v>
+      </c>
+      <c r="BM176">
+        <v>2.47</v>
+      </c>
+      <c r="BN176">
+        <v>1.51</v>
+      </c>
+      <c r="BO176">
+        <v>3.35</v>
+      </c>
+      <c r="BP176">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:68">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>7469038</v>
+      </c>
+      <c r="C177" t="s">
+        <v>68</v>
+      </c>
+      <c r="D177" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F177">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>78</v>
+      </c>
+      <c r="H177" t="s">
+        <v>74</v>
+      </c>
+      <c r="I177">
+        <v>1</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177">
+        <v>3</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>3</v>
+      </c>
+      <c r="O177" t="s">
+        <v>210</v>
+      </c>
+      <c r="P177" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q177">
+        <v>2.25</v>
+      </c>
+      <c r="R177">
+        <v>2.15</v>
+      </c>
+      <c r="S177">
+        <v>5</v>
+      </c>
+      <c r="T177">
+        <v>1.41</v>
+      </c>
+      <c r="U177">
+        <v>2.7</v>
+      </c>
+      <c r="V177">
+        <v>2.85</v>
+      </c>
+      <c r="W177">
+        <v>1.37</v>
+      </c>
+      <c r="X177">
+        <v>6.95</v>
+      </c>
+      <c r="Y177">
+        <v>1.07</v>
+      </c>
+      <c r="Z177">
+        <v>1.62</v>
+      </c>
+      <c r="AA177">
+        <v>3.8</v>
+      </c>
+      <c r="AB177">
+        <v>5.2</v>
+      </c>
+      <c r="AC177">
+        <v>1.06</v>
+      </c>
+      <c r="AD177">
+        <v>8.5</v>
+      </c>
+      <c r="AE177">
+        <v>1.3</v>
+      </c>
+      <c r="AF177">
+        <v>3.3</v>
+      </c>
+      <c r="AG177">
+        <v>1.95</v>
+      </c>
+      <c r="AH177">
+        <v>1.79</v>
+      </c>
+      <c r="AI177">
+        <v>1.9</v>
+      </c>
+      <c r="AJ177">
+        <v>1.83</v>
+      </c>
+      <c r="AK177">
+        <v>1.11</v>
+      </c>
+      <c r="AL177">
+        <v>1.22</v>
+      </c>
+      <c r="AM177">
+        <v>2.15</v>
+      </c>
+      <c r="AN177">
+        <v>2.2</v>
+      </c>
+      <c r="AO177">
+        <v>0.78</v>
+      </c>
+      <c r="AP177">
+        <v>2.27</v>
+      </c>
+      <c r="AQ177">
+        <v>0.7</v>
+      </c>
+      <c r="AR177">
+        <v>1.6</v>
+      </c>
+      <c r="AS177">
+        <v>1.47</v>
+      </c>
+      <c r="AT177">
+        <v>3.07</v>
+      </c>
+      <c r="AU177">
+        <v>11</v>
+      </c>
+      <c r="AV177">
+        <v>0</v>
+      </c>
+      <c r="AW177">
+        <v>10</v>
+      </c>
+      <c r="AX177">
+        <v>11</v>
+      </c>
+      <c r="AY177">
+        <v>21</v>
+      </c>
+      <c r="AZ177">
+        <v>11</v>
+      </c>
+      <c r="BA177">
+        <v>4</v>
+      </c>
+      <c r="BB177">
+        <v>2</v>
+      </c>
+      <c r="BC177">
+        <v>6</v>
+      </c>
+      <c r="BD177">
+        <v>1.54</v>
+      </c>
+      <c r="BE177">
+        <v>6.5</v>
+      </c>
+      <c r="BF177">
+        <v>2.8</v>
+      </c>
+      <c r="BG177">
+        <v>1.46</v>
+      </c>
+      <c r="BH177">
+        <v>2.48</v>
+      </c>
+      <c r="BI177">
+        <v>1.76</v>
+      </c>
+      <c r="BJ177">
+        <v>1.93</v>
+      </c>
+      <c r="BK177">
+        <v>2.23</v>
+      </c>
+      <c r="BL177">
+        <v>1.56</v>
+      </c>
+      <c r="BM177">
+        <v>2.9</v>
+      </c>
+      <c r="BN177">
+        <v>1.35</v>
+      </c>
+      <c r="BO177">
+        <v>3.9</v>
+      </c>
+      <c r="BP177">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="178" spans="1:68">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>7469037</v>
+      </c>
+      <c r="C178" t="s">
+        <v>68</v>
+      </c>
+      <c r="D178" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45681.66666666666</v>
+      </c>
+      <c r="F178">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>76</v>
+      </c>
+      <c r="H178" t="s">
+        <v>75</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>1</v>
+      </c>
+      <c r="O178" t="s">
+        <v>90</v>
+      </c>
+      <c r="P178" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q178">
+        <v>3.25</v>
+      </c>
+      <c r="R178">
+        <v>2.1</v>
+      </c>
+      <c r="S178">
+        <v>3</v>
+      </c>
+      <c r="T178">
+        <v>1.38</v>
+      </c>
+      <c r="U178">
+        <v>2.8</v>
+      </c>
+      <c r="V178">
+        <v>2.65</v>
+      </c>
+      <c r="W178">
+        <v>1.42</v>
+      </c>
+      <c r="X178">
+        <v>6.7</v>
+      </c>
+      <c r="Y178">
+        <v>1.07</v>
+      </c>
+      <c r="Z178">
+        <v>2.66</v>
+      </c>
+      <c r="AA178">
+        <v>3.35</v>
+      </c>
+      <c r="AB178">
+        <v>2.53</v>
+      </c>
+      <c r="AC178">
+        <v>1.06</v>
+      </c>
+      <c r="AD178">
+        <v>8.5</v>
+      </c>
+      <c r="AE178">
+        <v>1.3</v>
+      </c>
+      <c r="AF178">
+        <v>3.45</v>
+      </c>
+      <c r="AG178">
+        <v>1.77</v>
+      </c>
+      <c r="AH178">
+        <v>1.98</v>
+      </c>
+      <c r="AI178">
+        <v>1.65</v>
+      </c>
+      <c r="AJ178">
+        <v>2.05</v>
+      </c>
+      <c r="AK178">
+        <v>1.5</v>
+      </c>
+      <c r="AL178">
+        <v>1.28</v>
+      </c>
+      <c r="AM178">
+        <v>1.42</v>
+      </c>
+      <c r="AN178">
+        <v>1.1</v>
+      </c>
+      <c r="AO178">
+        <v>1.33</v>
+      </c>
+      <c r="AP178">
+        <v>1</v>
+      </c>
+      <c r="AQ178">
+        <v>1.5</v>
+      </c>
+      <c r="AR178">
+        <v>1.34</v>
+      </c>
+      <c r="AS178">
+        <v>1.4</v>
+      </c>
+      <c r="AT178">
+        <v>2.74</v>
+      </c>
+      <c r="AU178">
+        <v>4</v>
+      </c>
+      <c r="AV178">
+        <v>2</v>
+      </c>
+      <c r="AW178">
+        <v>6</v>
+      </c>
+      <c r="AX178">
+        <v>8</v>
+      </c>
+      <c r="AY178">
+        <v>10</v>
+      </c>
+      <c r="AZ178">
+        <v>10</v>
+      </c>
+      <c r="BA178">
+        <v>3</v>
+      </c>
+      <c r="BB178">
+        <v>3</v>
+      </c>
+      <c r="BC178">
+        <v>6</v>
+      </c>
+      <c r="BD178">
+        <v>2.07</v>
+      </c>
+      <c r="BE178">
+        <v>6.4</v>
+      </c>
+      <c r="BF178">
+        <v>1.95</v>
+      </c>
+      <c r="BG178">
+        <v>1.38</v>
+      </c>
+      <c r="BH178">
+        <v>2.8</v>
+      </c>
+      <c r="BI178">
+        <v>1.65</v>
+      </c>
+      <c r="BJ178">
+        <v>2.1</v>
+      </c>
+      <c r="BK178">
+        <v>2.02</v>
+      </c>
+      <c r="BL178">
+        <v>1.68</v>
+      </c>
+      <c r="BM178">
+        <v>2.55</v>
+      </c>
+      <c r="BN178">
+        <v>1.43</v>
+      </c>
+      <c r="BO178">
+        <v>3.45</v>
+      </c>
+      <c r="BP178">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
